--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L46" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G77" t="n">

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -856,12 +856,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05:35</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Adelaide United</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Macarthur</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -948,10 +948,10 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>46052.23263888889</v>
+        <v>46052.22916666666</v>
       </c>
     </row>
     <row r="5">
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>05:35</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Adelaide United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Macarthur</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>46052.3125</v>
+        <v>46052.23263888889</v>
       </c>
     </row>
     <row r="6">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>46052.33333333334</v>
+        <v>46052.3125</v>
       </c>
     </row>
     <row r="7">
@@ -1213,27 +1213,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>46052.35416666666</v>
+        <v>46052.33333333334</v>
       </c>
     </row>
     <row r="8">
@@ -1332,27 +1332,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46052.375</v>
+        <v>46052.35416666666</v>
       </c>
     </row>
     <row r="9">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G77" t="n">

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G77" t="n">

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="M66" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="N66" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G75" t="n">

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2257,10 +2257,10 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.32</v>
+        <v>1.9</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="N19" t="n">
-        <v>9</v>
+        <v>3.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4625,10 +4625,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="N36" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,10 +4744,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5772,17 +5772,17 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.93</v>
+        <v>2.77</v>
       </c>
       <c r="M74" t="n">
-        <v>3.32</v>
+        <v>3.05</v>
       </c>
       <c r="N74" t="n">
-        <v>2.43</v>
+        <v>2.32</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="M76" t="n">
         <v>3.3</v>
       </c>
       <c r="N76" t="n">
-        <v>4.05</v>
+        <v>3.77</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,7 +9510,7 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AB76" t="n">
         <v>1.7</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4506,10 +4506,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4625,10 +4625,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="M36" t="n">
-        <v>2.95</v>
+        <v>3.27</v>
       </c>
       <c r="N36" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,16 +4744,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.64</v>
+        <v>3.3</v>
       </c>
       <c r="M37" t="n">
-        <v>3.27</v>
+        <v>2.75</v>
       </c>
       <c r="N37" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4863,16 +4863,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L39" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,17 +5296,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="M44" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N44" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="M55" t="n">
-        <v>3.35</v>
+        <v>3.01</v>
       </c>
       <c r="N55" t="n">
-        <v>2.75</v>
+        <v>3.57</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.97</v>
+        <v>2.56</v>
       </c>
       <c r="M57" t="n">
-        <v>3.01</v>
+        <v>3.2</v>
       </c>
       <c r="N57" t="n">
-        <v>3.57</v>
+        <v>2.4</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="M58" t="n">
         <v>3.2</v>
       </c>
       <c r="N58" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="M59" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N59" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="M62" t="n">
         <v>3.45</v>
       </c>
       <c r="N62" t="n">
-        <v>2.12</v>
+        <v>1.86</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.66</v>
+        <v>3.73</v>
       </c>
       <c r="M65" t="n">
-        <v>3.52</v>
+        <v>3.07</v>
       </c>
       <c r="N65" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.88</v>
+        <v>2.41</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.85</v>
+        <v>3.3</v>
       </c>
       <c r="M34" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="N34" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4506,10 +4506,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.3</v>
+        <v>1.85</v>
       </c>
       <c r="M37" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="N37" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4863,10 +4863,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.91</v>
+        <v>2.55</v>
       </c>
       <c r="M45" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="N45" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.35</v>
+        <v>1.91</v>
       </c>
       <c r="M47" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N47" t="n">
-        <v>2.08</v>
+        <v>3.75</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.6</v>
+        <v>2.21</v>
       </c>
       <c r="M48" t="n">
-        <v>3.4</v>
+        <v>2.84</v>
       </c>
       <c r="N48" t="n">
-        <v>1.98</v>
+        <v>3.16</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.38</v>
+        <v>3.6</v>
       </c>
       <c r="M54" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N54" t="n">
-        <v>2.75</v>
+        <v>1.98</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="M57" t="n">
         <v>3.2</v>
       </c>
       <c r="N57" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="M58" t="n">
         <v>3.2</v>
       </c>
       <c r="N58" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.31</v>
+        <v>1.97</v>
       </c>
       <c r="M59" t="n">
-        <v>3.3</v>
+        <v>3.01</v>
       </c>
       <c r="N59" t="n">
-        <v>2.9</v>
+        <v>3.57</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.7</v>
+        <v>1.66</v>
       </c>
       <c r="M68" t="n">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="N68" t="n">
-        <v>2.01</v>
+        <v>4.3</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.66</v>
+        <v>2.22</v>
       </c>
       <c r="M69" t="n">
-        <v>3.52</v>
+        <v>3.56</v>
       </c>
       <c r="N69" t="n">
-        <v>4.3</v>
+        <v>2.95</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.82</v>
+        <v>2.35</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.77</v>
+        <v>1.92</v>
       </c>
       <c r="M73" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="N73" t="n">
-        <v>2.32</v>
+        <v>3.8</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.3</v>
+        <v>1.85</v>
       </c>
       <c r="M34" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="N34" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4506,10 +4506,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4625,10 +4625,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4863,10 +4863,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.29</v>
+        <v>3.35</v>
       </c>
       <c r="M42" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="N42" t="n">
-        <v>3.2</v>
+        <v>2.08</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="M45" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="N45" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="M46" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N46" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="M47" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N47" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.21</v>
+        <v>4.1</v>
       </c>
       <c r="M48" t="n">
-        <v>2.84</v>
+        <v>3.45</v>
       </c>
       <c r="N48" t="n">
-        <v>3.16</v>
+        <v>1.86</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.52</v>
+        <v>1.91</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="M57" t="n">
         <v>3.2</v>
       </c>
       <c r="N57" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.97</v>
+        <v>2.38</v>
       </c>
       <c r="M59" t="n">
-        <v>3.01</v>
+        <v>3.35</v>
       </c>
       <c r="N59" t="n">
-        <v>3.57</v>
+        <v>2.75</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="M60" t="n">
-        <v>3.35</v>
+        <v>2.84</v>
       </c>
       <c r="N60" t="n">
-        <v>2.75</v>
+        <v>3.16</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="M61" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N61" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.7</v>
+        <v>1.66</v>
       </c>
       <c r="M71" t="n">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="N71" t="n">
-        <v>2.01</v>
+        <v>4.3</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.77</v>
+        <v>1.92</v>
       </c>
       <c r="M75" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="N75" t="n">
-        <v>2.32</v>
+        <v>3.8</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.97</v>
+        <v>3.2</v>
       </c>
       <c r="M30" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="N30" t="n">
-        <v>3.55</v>
+        <v>2.06</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4042,10 +4042,10 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.2</v>
+        <v>1.97</v>
       </c>
       <c r="M33" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="N33" t="n">
-        <v>2.06</v>
+        <v>3.55</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L41" t="n">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="M46" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N46" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="M47" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N47" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>4.1</v>
+        <v>2.21</v>
       </c>
       <c r="M48" t="n">
-        <v>3.45</v>
+        <v>2.84</v>
       </c>
       <c r="N48" t="n">
-        <v>1.86</v>
+        <v>3.16</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.91</v>
+        <v>1.52</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.56</v>
+        <v>2.15</v>
       </c>
       <c r="M57" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N57" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="M59" t="n">
-        <v>3.35</v>
+        <v>3.01</v>
       </c>
       <c r="N59" t="n">
-        <v>2.75</v>
+        <v>3.57</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="M60" t="n">
-        <v>2.84</v>
+        <v>3.6</v>
       </c>
       <c r="N60" t="n">
-        <v>3.16</v>
+        <v>2.75</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.52</v>
+        <v>2.02</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="M61" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N61" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.73</v>
+        <v>2.22</v>
       </c>
       <c r="M70" t="n">
-        <v>3.07</v>
+        <v>3.56</v>
       </c>
       <c r="N70" t="n">
-        <v>2.1</v>
+        <v>2.95</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.41</v>
+        <v>1.6</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.57</v>
+        <v>2.35</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.66</v>
+        <v>3.73</v>
       </c>
       <c r="M71" t="n">
-        <v>3.52</v>
+        <v>3.07</v>
       </c>
       <c r="N71" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.88</v>
+        <v>2.41</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="M72" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="N72" t="n">
-        <v>4.01</v>
+        <v>3.8</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.77</v>
+        <v>1.91</v>
       </c>
       <c r="M74" t="n">
         <v>3.05</v>
       </c>
       <c r="N74" t="n">
-        <v>2.32</v>
+        <v>4.01</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.92</v>
+        <v>2.77</v>
       </c>
       <c r="M75" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="N75" t="n">
-        <v>3.8</v>
+        <v>2.32</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.85</v>
+        <v>3.3</v>
       </c>
       <c r="M34" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="N34" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4506,10 +4506,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4625,10 +4625,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="M36" t="n">
-        <v>3.27</v>
+        <v>2.95</v>
       </c>
       <c r="N36" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,16 +4744,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,17 +5177,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.35</v>
+        <v>1.91</v>
       </c>
       <c r="M42" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N42" t="n">
-        <v>2.08</v>
+        <v>3.75</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5653,17 +5653,17 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.29</v>
+        <v>1.96</v>
       </c>
       <c r="M45" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="N45" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.96</v>
+        <v>2.29</v>
       </c>
       <c r="M46" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="N46" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.15</v>
+        <v>2.15</v>
       </c>
       <c r="M50" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N50" t="n">
-        <v>2.12</v>
+        <v>3.25</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.97</v>
+        <v>3.15</v>
       </c>
       <c r="M59" t="n">
-        <v>3.01</v>
+        <v>3.45</v>
       </c>
       <c r="N59" t="n">
-        <v>3.57</v>
+        <v>2.12</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="M60" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N60" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>4.1</v>
+        <v>2.35</v>
       </c>
       <c r="M61" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N61" t="n">
-        <v>1.86</v>
+        <v>2.75</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.91</v>
+        <v>2.77</v>
       </c>
       <c r="M74" t="n">
         <v>3.05</v>
       </c>
       <c r="N74" t="n">
-        <v>4.01</v>
+        <v>2.32</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.77</v>
+        <v>1.91</v>
       </c>
       <c r="M75" t="n">
         <v>3.05</v>
       </c>
       <c r="N75" t="n">
-        <v>2.32</v>
+        <v>4.01</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4042,10 +4042,10 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4399,10 +4399,10 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.3</v>
+        <v>1.85</v>
       </c>
       <c r="M34" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="N34" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4506,10 +4506,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4625,10 +4625,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="M36" t="n">
-        <v>2.95</v>
+        <v>3.27</v>
       </c>
       <c r="N36" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,16 +4744,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.35</v>
+        <v>2.29</v>
       </c>
       <c r="M41" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="N41" t="n">
-        <v>2.08</v>
+        <v>3.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.91</v>
+        <v>3.35</v>
       </c>
       <c r="M42" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N42" t="n">
-        <v>3.75</v>
+        <v>2.08</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5772,17 +5772,17 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.29</v>
+        <v>1.96</v>
       </c>
       <c r="M46" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="N46" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="M56" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N56" t="n">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.15</v>
+        <v>2.35</v>
       </c>
       <c r="M59" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N59" t="n">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="M60" t="n">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="N60" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.35</v>
+        <v>3.6</v>
       </c>
       <c r="M61" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="N61" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB61" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.73</v>
+        <v>1.66</v>
       </c>
       <c r="M71" t="n">
-        <v>3.07</v>
+        <v>3.52</v>
       </c>
       <c r="N71" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>2.41</v>
+        <v>1.88</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.77</v>
+        <v>1.91</v>
       </c>
       <c r="M74" t="n">
         <v>3.05</v>
       </c>
       <c r="N74" t="n">
-        <v>2.32</v>
+        <v>4.01</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.91</v>
+        <v>2.77</v>
       </c>
       <c r="M75" t="n">
         <v>3.05</v>
       </c>
       <c r="N75" t="n">
-        <v>4.01</v>
+        <v>2.32</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.27</v>
+        <v>1.9</v>
       </c>
       <c r="M18" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="N18" t="n">
-        <v>8.6</v>
+        <v>3.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.85</v>
+        <v>3.3</v>
       </c>
       <c r="M34" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="N34" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4506,10 +4506,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.3</v>
+        <v>1.85</v>
       </c>
       <c r="M35" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="N35" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4625,10 +4625,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.29</v>
+        <v>1.91</v>
       </c>
       <c r="M41" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="N41" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.35</v>
+        <v>2.29</v>
       </c>
       <c r="M42" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="N42" t="n">
-        <v>2.08</v>
+        <v>3.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5772,17 +5772,17 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,17 +6010,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="M60" t="n">
-        <v>2.84</v>
+        <v>3.6</v>
       </c>
       <c r="N60" t="n">
-        <v>3.16</v>
+        <v>2.75</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.52</v>
+        <v>2.02</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.6</v>
+        <v>1.97</v>
       </c>
       <c r="M61" t="n">
-        <v>3.65</v>
+        <v>3.01</v>
       </c>
       <c r="N61" t="n">
-        <v>1.95</v>
+        <v>3.57</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="M62" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="N62" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.73</v>
+        <v>1.66</v>
       </c>
       <c r="M68" t="n">
-        <v>3.07</v>
+        <v>3.52</v>
       </c>
       <c r="N68" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.41</v>
+        <v>1.88</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.66</v>
+        <v>2.22</v>
       </c>
       <c r="M71" t="n">
-        <v>3.52</v>
+        <v>3.56</v>
       </c>
       <c r="N71" t="n">
-        <v>4.3</v>
+        <v>2.95</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.82</v>
+        <v>2.35</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="M72" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="N72" t="n">
-        <v>3.8</v>
+        <v>4.01</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.27</v>
+        <v>1.9</v>
       </c>
       <c r="M19" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="N19" t="n">
-        <v>8.6</v>
+        <v>3.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4506,10 +4506,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.64</v>
+        <v>3.3</v>
       </c>
       <c r="M36" t="n">
-        <v>3.27</v>
+        <v>2.75</v>
       </c>
       <c r="N36" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,16 +4744,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="M41" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.35</v>
+        <v>2.29</v>
       </c>
       <c r="M43" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="N43" t="n">
-        <v>2.08</v>
+        <v>3.2</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="M50" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N50" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.15</v>
+        <v>2.56</v>
       </c>
       <c r="M51" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N51" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="M54" t="n">
         <v>3.45</v>
       </c>
       <c r="N54" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.56</v>
+        <v>2.31</v>
       </c>
       <c r="M57" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N57" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="M66" t="n">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="N66" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.66</v>
+        <v>2.22</v>
       </c>
       <c r="M68" t="n">
-        <v>3.52</v>
+        <v>3.56</v>
       </c>
       <c r="N68" t="n">
-        <v>4.3</v>
+        <v>2.95</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.82</v>
+        <v>2.35</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.27</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="N17" t="n">
-        <v>8.6</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.9</v>
+        <v>1.27</v>
       </c>
       <c r="M19" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="N19" t="n">
-        <v>3.8</v>
+        <v>8.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.16</v>
+        <v>4.7</v>
       </c>
       <c r="M26" t="n">
-        <v>3.19</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>2.91</v>
+        <v>1.7</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.97</v>
+        <v>3.35</v>
       </c>
       <c r="M32" t="n">
-        <v>3.55</v>
+        <v>3.67</v>
       </c>
       <c r="N32" t="n">
-        <v>3.55</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.2</v>
+        <v>1.92</v>
       </c>
       <c r="M33" t="n">
-        <v>3.65</v>
+        <v>3.53</v>
       </c>
       <c r="N33" t="n">
-        <v>2.06</v>
+        <v>3.76</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,17 +5177,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="M41" t="n">
-        <v>3.1</v>
+        <v>3.37</v>
       </c>
       <c r="N41" t="n">
-        <v>3.7</v>
+        <v>2.66</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.29</v>
+        <v>3.35</v>
       </c>
       <c r="M43" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="N43" t="n">
-        <v>3.2</v>
+        <v>2.08</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.35</v>
+        <v>2.34</v>
       </c>
       <c r="M44" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N44" t="n">
-        <v>2.08</v>
+        <v>3.05</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,17 +6010,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="M48" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="N48" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.7</v>
+        <v>2.01</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.02</v>
+        <v>1.71</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.97</v>
+        <v>2.13</v>
       </c>
       <c r="M49" t="n">
-        <v>3.01</v>
+        <v>3.08</v>
       </c>
       <c r="N49" t="n">
-        <v>3.57</v>
+        <v>3.08</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="M50" t="n">
-        <v>3.4</v>
+        <v>3.01</v>
       </c>
       <c r="N50" t="n">
-        <v>3.25</v>
+        <v>3.57</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="M51" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N51" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.01</v>
+        <v>1.86</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.15</v>
+        <v>2.21</v>
       </c>
       <c r="M54" t="n">
-        <v>3.45</v>
+        <v>2.84</v>
       </c>
       <c r="N54" t="n">
-        <v>2.12</v>
+        <v>3.16</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.31</v>
+        <v>3.15</v>
       </c>
       <c r="M57" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N57" t="n">
-        <v>2.9</v>
+        <v>2.12</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="M66" t="n">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
       <c r="N66" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.66</v>
+        <v>2.22</v>
       </c>
       <c r="M69" t="n">
-        <v>3.52</v>
+        <v>3.56</v>
       </c>
       <c r="N69" t="n">
-        <v>4.3</v>
+        <v>2.95</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.82</v>
+        <v>2.35</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="M73" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N73" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="M74" t="n">
-        <v>3.05</v>
+        <v>3.29</v>
       </c>
       <c r="N74" t="n">
-        <v>4.01</v>
+        <v>4.4</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.77</v>
+        <v>1.39</v>
       </c>
       <c r="M75" t="n">
-        <v>3.05</v>
+        <v>4.75</v>
       </c>
       <c r="N75" t="n">
-        <v>2.32</v>
+        <v>7.3</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI79"/>
+  <dimension ref="A1:AI80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.35</v>
+        <v>1.92</v>
       </c>
       <c r="M32" t="n">
-        <v>3.67</v>
+        <v>3.53</v>
       </c>
       <c r="N32" t="n">
-        <v>2</v>
+        <v>3.76</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="M38" t="n">
-        <v>2.85</v>
+        <v>3.37</v>
       </c>
       <c r="N38" t="n">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,17 +5177,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.41</v>
+        <v>2.29</v>
       </c>
       <c r="M42" t="n">
-        <v>4.05</v>
+        <v>2.85</v>
       </c>
       <c r="N42" t="n">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.35</v>
+        <v>2.55</v>
       </c>
       <c r="M43" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N43" t="n">
-        <v>2.08</v>
+        <v>2.75</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.55</v>
+        <v>3.35</v>
       </c>
       <c r="M45" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N45" t="n">
-        <v>2.75</v>
+        <v>2.08</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.96</v>
+        <v>1.41</v>
       </c>
       <c r="M47" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="N47" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6092,12 +6092,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6202,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="AI48" s="3" t="n">
-        <v>46052.66666666666</v>
+        <v>46052.65625</v>
       </c>
     </row>
     <row r="49">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.13</v>
+        <v>1.97</v>
       </c>
       <c r="M49" t="n">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="N49" t="n">
-        <v>3.08</v>
+        <v>3.57</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="M50" t="n">
-        <v>3.01</v>
+        <v>3.25</v>
       </c>
       <c r="N50" t="n">
-        <v>3.57</v>
+        <v>2.65</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="M51" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N51" t="n">
-        <v>2.65</v>
+        <v>2.12</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="M53" t="n">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="N53" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.21</v>
+        <v>3.39</v>
       </c>
       <c r="M54" t="n">
-        <v>2.84</v>
+        <v>3.23</v>
       </c>
       <c r="N54" t="n">
-        <v>3.16</v>
+        <v>1.94</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7877,12 +7877,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.42</v>
+        <v>4.1</v>
       </c>
       <c r="M63" t="n">
-        <v>3.12</v>
+        <v>3.45</v>
       </c>
       <c r="N63" t="n">
-        <v>2.59</v>
+        <v>1.86</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7966,7 +7966,7 @@
         <v>1.83</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -7987,7 +7987,7 @@
         <v>0</v>
       </c>
       <c r="AI63" s="3" t="n">
-        <v>46052.67708333334</v>
+        <v>46052.66666666666</v>
       </c>
     </row>
     <row r="64">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="AI65" s="3" t="n">
-        <v>46052.6875</v>
+        <v>46052.67708333334</v>
       </c>
     </row>
     <row r="66">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.65</v>
+        <v>1.66</v>
       </c>
       <c r="M66" t="n">
-        <v>3.29</v>
+        <v>3.52</v>
       </c>
       <c r="N66" t="n">
-        <v>2.03</v>
+        <v>4.3</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,55 +8870,55 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.73</v>
+        <v>3.65</v>
       </c>
       <c r="M71" t="n">
-        <v>3.07</v>
+        <v>3.29</v>
       </c>
       <c r="N71" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA71" t="n">
         <v>2.1</v>
       </c>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" t="n">
-        <v>0</v>
-      </c>
-      <c r="V71" t="n">
-        <v>0</v>
-      </c>
-      <c r="W71" t="n">
-        <v>0</v>
-      </c>
-      <c r="X71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA71" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AB71" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8948,12 +8948,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.77</v>
+        <v>2.22</v>
       </c>
       <c r="M72" t="n">
-        <v>3.05</v>
+        <v>3.56</v>
       </c>
       <c r="N72" t="n">
-        <v>2.32</v>
+        <v>2.95</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.81</v>
+        <v>2.35</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9058,7 +9058,7 @@
         <v>0</v>
       </c>
       <c r="AI72" s="3" t="n">
-        <v>46052.69791666666</v>
+        <v>46052.6875</v>
       </c>
     </row>
     <row r="73">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.68</v>
+        <v>1.39</v>
       </c>
       <c r="M73" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="N73" t="n">
-        <v>4.7</v>
+        <v>7.3</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="M74" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="N74" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.39</v>
+        <v>2.77</v>
       </c>
       <c r="M75" t="n">
-        <v>4.75</v>
+        <v>3.05</v>
       </c>
       <c r="N75" t="n">
-        <v>7.3</v>
+        <v>2.32</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9424,12 +9424,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="M76" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="N76" t="n">
-        <v>3.77</v>
+        <v>4.4</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
         <v>0</v>
       </c>
       <c r="AI76" s="3" t="n">
-        <v>46052.70833333334</v>
+        <v>46052.69791666666</v>
       </c>
     </row>
     <row r="77">
@@ -9662,12 +9662,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9772,7 +9772,7 @@
         <v>0</v>
       </c>
       <c r="AI78" s="3" t="n">
-        <v>46052.73958333334</v>
+        <v>46052.70833333334</v>
       </c>
     </row>
     <row r="79">
@@ -9781,116 +9781,235 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Vitória Guimarães</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Moreirense FC</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI79" s="3" t="n">
+        <v>46052.73958333334</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Chile Primera División</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>Universidad Chile</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Audax Italiano</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" t="inlineStr">
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" t="n">
-        <v>0</v>
-      </c>
-      <c r="V79" t="n">
-        <v>0</v>
-      </c>
-      <c r="W79" t="n">
-        <v>0</v>
-      </c>
-      <c r="X79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA79" t="n">
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA80" t="n">
         <v>1.65</v>
       </c>
-      <c r="AB79" t="n">
+      <c r="AB80" t="n">
         <v>2.2</v>
       </c>
-      <c r="AC79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI79" s="3" t="n">
+      <c r="AC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI80" s="3" t="n">
         <v>46052.83333333334</v>
       </c>
     </row>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.9</v>
+        <v>1.27</v>
       </c>
       <c r="M16" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="N16" t="n">
-        <v>3.8</v>
+        <v>8.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.27</v>
+        <v>1.9</v>
       </c>
       <c r="M19" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="N19" t="n">
-        <v>8.6</v>
+        <v>3.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.92</v>
+        <v>3.35</v>
       </c>
       <c r="M32" t="n">
-        <v>3.53</v>
+        <v>3.67</v>
       </c>
       <c r="N32" t="n">
-        <v>3.76</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4506,10 +4506,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4625,10 +4625,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.3</v>
+        <v>1.85</v>
       </c>
       <c r="M36" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="N36" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,10 +4744,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="M38" t="n">
-        <v>3.37</v>
+        <v>2.95</v>
       </c>
       <c r="N38" t="n">
-        <v>2.66</v>
+        <v>3.05</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,17 +5058,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.96</v>
+        <v>3.35</v>
       </c>
       <c r="M40" t="n">
         <v>3.1</v>
       </c>
       <c r="N40" t="n">
-        <v>3.7</v>
+        <v>2.08</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5415,17 +5415,17 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.55</v>
+        <v>2.24</v>
       </c>
       <c r="M43" t="n">
-        <v>2.95</v>
+        <v>3.37</v>
       </c>
       <c r="N43" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="M44" t="n">
         <v>2.95</v>
       </c>
       <c r="N44" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="M53" t="n">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="N53" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.13</v>
+        <v>1.97</v>
       </c>
       <c r="M55" t="n">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="N55" t="n">
-        <v>3.08</v>
+        <v>3.57</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.56</v>
+        <v>3.15</v>
       </c>
       <c r="M56" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N56" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.66</v>
+        <v>3.65</v>
       </c>
       <c r="M66" t="n">
-        <v>3.52</v>
+        <v>3.29</v>
       </c>
       <c r="N66" t="n">
-        <v>4.3</v>
+        <v>2.03</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.65</v>
+        <v>1.66</v>
       </c>
       <c r="M71" t="n">
-        <v>3.29</v>
+        <v>3.52</v>
       </c>
       <c r="N71" t="n">
-        <v>2.03</v>
+        <v>4.3</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.39</v>
+        <v>1.68</v>
       </c>
       <c r="M73" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="N73" t="n">
-        <v>7.3</v>
+        <v>4.7</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB73" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.68</v>
+        <v>2.77</v>
       </c>
       <c r="M74" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="N74" t="n">
-        <v>4.7</v>
+        <v>2.32</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.77</v>
+        <v>1.39</v>
       </c>
       <c r="M75" t="n">
-        <v>3.05</v>
+        <v>4.75</v>
       </c>
       <c r="N75" t="n">
-        <v>2.32</v>
+        <v>7.3</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4506,10 +4506,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4625,10 +4625,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="M36" t="n">
-        <v>2.95</v>
+        <v>3.27</v>
       </c>
       <c r="N36" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,16 +4744,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.64</v>
+        <v>3.3</v>
       </c>
       <c r="M37" t="n">
-        <v>3.27</v>
+        <v>2.75</v>
       </c>
       <c r="N37" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4863,16 +4863,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="M38" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="N38" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="M39" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N39" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5415,17 +5415,17 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.24</v>
+        <v>1.91</v>
       </c>
       <c r="M43" t="n">
-        <v>3.37</v>
+        <v>3.2</v>
       </c>
       <c r="N43" t="n">
-        <v>2.66</v>
+        <v>3.75</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.55</v>
+        <v>2.24</v>
       </c>
       <c r="M44" t="n">
-        <v>2.95</v>
+        <v>3.37</v>
       </c>
       <c r="N44" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,17 +5891,17 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.15</v>
+        <v>2.31</v>
       </c>
       <c r="M56" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N56" t="n">
-        <v>2.12</v>
+        <v>2.9</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.21</v>
+        <v>2.56</v>
       </c>
       <c r="M59" t="n">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="N59" t="n">
-        <v>3.16</v>
+        <v>2.4</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.35</v>
+        <v>2.01</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.39</v>
+        <v>2.21</v>
       </c>
       <c r="M61" t="n">
-        <v>3.23</v>
+        <v>2.84</v>
       </c>
       <c r="N61" t="n">
-        <v>1.94</v>
+        <v>3.16</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.3</v>
+        <v>3.39</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="N62" t="n">
-        <v>2.65</v>
+        <v>1.94</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.65</v>
+        <v>2.22</v>
       </c>
       <c r="M66" t="n">
-        <v>3.29</v>
+        <v>3.56</v>
       </c>
       <c r="N66" t="n">
-        <v>2.03</v>
+        <v>2.95</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.22</v>
+        <v>1.66</v>
       </c>
       <c r="M72" t="n">
-        <v>3.56</v>
+        <v>3.52</v>
       </c>
       <c r="N72" t="n">
-        <v>2.95</v>
+        <v>4.3</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="AB72" t="n">
-        <v>2.35</v>
+        <v>1.82</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.68</v>
+        <v>2.77</v>
       </c>
       <c r="M73" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="N73" t="n">
-        <v>4.7</v>
+        <v>2.32</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.77</v>
+        <v>1.68</v>
       </c>
       <c r="M74" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="N74" t="n">
-        <v>2.32</v>
+        <v>4.7</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.27</v>
+        <v>1.9</v>
       </c>
       <c r="M18" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="N18" t="n">
-        <v>8.6</v>
+        <v>3.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.9</v>
+        <v>1.27</v>
       </c>
       <c r="M19" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="N19" t="n">
-        <v>3.8</v>
+        <v>8.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.92</v>
+        <v>3.35</v>
       </c>
       <c r="M31" t="n">
-        <v>3.53</v>
+        <v>3.67</v>
       </c>
       <c r="N31" t="n">
-        <v>3.76</v>
+        <v>2</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4625,10 +4625,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.64</v>
+        <v>3.3</v>
       </c>
       <c r="M36" t="n">
-        <v>3.27</v>
+        <v>2.75</v>
       </c>
       <c r="N36" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,16 +4744,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.3</v>
+        <v>1.85</v>
       </c>
       <c r="M37" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="N37" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4863,10 +4863,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.34</v>
+        <v>3.35</v>
       </c>
       <c r="M39" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>3.05</v>
+        <v>2.08</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.35</v>
+        <v>2.24</v>
       </c>
       <c r="M40" t="n">
-        <v>3.1</v>
+        <v>3.37</v>
       </c>
       <c r="N40" t="n">
-        <v>2.08</v>
+        <v>2.66</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,17 +5296,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.91</v>
+        <v>2.55</v>
       </c>
       <c r="M43" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="N43" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="M45" t="n">
         <v>2.95</v>
       </c>
       <c r="N45" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,17 +5891,17 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>4.1</v>
+        <v>2.21</v>
       </c>
       <c r="M50" t="n">
-        <v>3.45</v>
+        <v>2.84</v>
       </c>
       <c r="N50" t="n">
-        <v>1.86</v>
+        <v>3.16</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.91</v>
+        <v>1.52</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="M63" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N63" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.22</v>
+        <v>3.65</v>
       </c>
       <c r="M66" t="n">
-        <v>3.56</v>
+        <v>3.29</v>
       </c>
       <c r="N66" t="n">
-        <v>2.95</v>
+        <v>2.03</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.73</v>
+        <v>1.66</v>
       </c>
       <c r="M67" t="n">
-        <v>3.07</v>
+        <v>3.52</v>
       </c>
       <c r="N67" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.66</v>
+        <v>3.73</v>
       </c>
       <c r="M72" t="n">
-        <v>3.52</v>
+        <v>3.07</v>
       </c>
       <c r="N72" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.77</v>
+        <v>1.68</v>
       </c>
       <c r="M73" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="N73" t="n">
-        <v>2.32</v>
+        <v>4.7</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.68</v>
+        <v>1.39</v>
       </c>
       <c r="M74" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="N74" t="n">
-        <v>4.7</v>
+        <v>7.3</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.39</v>
+        <v>2.77</v>
       </c>
       <c r="M75" t="n">
-        <v>4.75</v>
+        <v>3.05</v>
       </c>
       <c r="N75" t="n">
-        <v>7.3</v>
+        <v>2.32</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.3</v>
+        <v>1.85</v>
       </c>
       <c r="M36" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="N36" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,10 +4744,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.85</v>
+        <v>3.3</v>
       </c>
       <c r="M37" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="N37" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4863,10 +4863,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="M38" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N38" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,17 +5058,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,17 +5296,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.41</v>
+        <v>3.35</v>
       </c>
       <c r="M42" t="n">
-        <v>4.05</v>
+        <v>3.1</v>
       </c>
       <c r="N42" t="n">
-        <v>7</v>
+        <v>2.08</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="M43" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="N43" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.34</v>
+        <v>1.96</v>
       </c>
       <c r="M45" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N45" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.96</v>
+        <v>2.29</v>
       </c>
       <c r="M46" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="N46" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.91</v>
+        <v>3.2</v>
       </c>
       <c r="M47" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N47" t="n">
-        <v>3.75</v>
+        <v>2.12</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.97</v>
+        <v>3.39</v>
       </c>
       <c r="M49" t="n">
-        <v>3.01</v>
+        <v>3.23</v>
       </c>
       <c r="N49" t="n">
-        <v>3.57</v>
+        <v>1.94</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.15</v>
+        <v>1.97</v>
       </c>
       <c r="M54" t="n">
-        <v>3.45</v>
+        <v>3.01</v>
       </c>
       <c r="N54" t="n">
-        <v>2.12</v>
+        <v>3.57</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="M55" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="N55" t="n">
-        <v>3.08</v>
+        <v>2.65</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="M57" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="N57" t="n">
-        <v>2.65</v>
+        <v>3.16</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.84</v>
+        <v>1.52</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.56</v>
+        <v>3.15</v>
       </c>
       <c r="M59" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N59" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.65</v>
+        <v>3.73</v>
       </c>
       <c r="M66" t="n">
-        <v>3.29</v>
+        <v>3.07</v>
       </c>
       <c r="N66" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.73</v>
+        <v>1.66</v>
       </c>
       <c r="M72" t="n">
-        <v>3.07</v>
+        <v>3.52</v>
       </c>
       <c r="N72" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.39</v>
+        <v>2.77</v>
       </c>
       <c r="M74" t="n">
-        <v>4.75</v>
+        <v>3.05</v>
       </c>
       <c r="N74" t="n">
-        <v>7.3</v>
+        <v>2.32</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.77</v>
+        <v>1.39</v>
       </c>
       <c r="M75" t="n">
-        <v>3.05</v>
+        <v>4.75</v>
       </c>
       <c r="N75" t="n">
-        <v>2.32</v>
+        <v>7.3</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.64</v>
+        <v>3.3</v>
       </c>
       <c r="M34" t="n">
-        <v>3.27</v>
+        <v>2.75</v>
       </c>
       <c r="N34" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4506,16 +4506,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4863,10 +4863,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4939,17 +4939,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,17 +5058,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.35</v>
+        <v>1.91</v>
       </c>
       <c r="M42" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N42" t="n">
-        <v>2.08</v>
+        <v>3.75</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.91</v>
+        <v>2.34</v>
       </c>
       <c r="M43" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="N43" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="M44" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="N44" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.96</v>
+        <v>3.35</v>
       </c>
       <c r="M45" t="n">
         <v>3.1</v>
       </c>
       <c r="N45" t="n">
-        <v>3.7</v>
+        <v>2.08</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.29</v>
+        <v>3.2</v>
       </c>
       <c r="M46" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="N46" t="n">
-        <v>3.2</v>
+        <v>2.12</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="M47" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N47" t="n">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.39</v>
+        <v>4.1</v>
       </c>
       <c r="M49" t="n">
-        <v>3.23</v>
+        <v>3.45</v>
       </c>
       <c r="N49" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>4.1</v>
+        <v>2.31</v>
       </c>
       <c r="M58" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N58" t="n">
-        <v>1.86</v>
+        <v>2.9</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.15</v>
+        <v>1.97</v>
       </c>
       <c r="M59" t="n">
-        <v>3.45</v>
+        <v>3.01</v>
       </c>
       <c r="N59" t="n">
-        <v>2.12</v>
+        <v>3.57</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,14 +8037,14 @@
         </is>
       </c>
       <c r="L64" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M64" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N64" t="n">
         <v>2.59</v>
       </c>
-      <c r="M64" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="N64" t="n">
-        <v>2.53</v>
-      </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="M65" t="n">
-        <v>3.12</v>
+        <v>3.38</v>
       </c>
       <c r="N65" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.73</v>
+        <v>1.66</v>
       </c>
       <c r="M66" t="n">
-        <v>3.07</v>
+        <v>3.52</v>
       </c>
       <c r="N66" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.65</v>
+        <v>2.22</v>
       </c>
       <c r="M70" t="n">
-        <v>3.29</v>
+        <v>3.56</v>
       </c>
       <c r="N70" t="n">
-        <v>2.03</v>
+        <v>2.95</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.22</v>
+        <v>3.73</v>
       </c>
       <c r="M71" t="n">
-        <v>3.56</v>
+        <v>3.07</v>
       </c>
       <c r="N71" t="n">
-        <v>2.95</v>
+        <v>2.1</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB71" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>2.35</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.66</v>
+        <v>3.65</v>
       </c>
       <c r="M72" t="n">
-        <v>3.52</v>
+        <v>3.29</v>
       </c>
       <c r="N72" t="n">
-        <v>4.3</v>
+        <v>2.03</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="M73" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="N73" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.77</v>
+        <v>1.68</v>
       </c>
       <c r="M74" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="N74" t="n">
-        <v>2.32</v>
+        <v>4.7</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.39</v>
+        <v>2.77</v>
       </c>
       <c r="M75" t="n">
-        <v>4.75</v>
+        <v>3.05</v>
       </c>
       <c r="N75" t="n">
-        <v>7.3</v>
+        <v>2.32</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.85</v>
+        <v>1.39</v>
       </c>
       <c r="M76" t="n">
-        <v>3.29</v>
+        <v>4.75</v>
       </c>
       <c r="N76" t="n">
-        <v>4.4</v>
+        <v>7.3</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.27</v>
+        <v>1.9</v>
       </c>
       <c r="M18" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="N18" t="n">
-        <v>8.6</v>
+        <v>3.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.92</v>
+        <v>3.35</v>
       </c>
       <c r="M31" t="n">
-        <v>3.53</v>
+        <v>3.67</v>
       </c>
       <c r="N31" t="n">
-        <v>3.76</v>
+        <v>2</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.3</v>
+        <v>1.85</v>
       </c>
       <c r="M34" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="N34" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4506,10 +4506,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.64</v>
+        <v>3.3</v>
       </c>
       <c r="M35" t="n">
-        <v>3.27</v>
+        <v>2.75</v>
       </c>
       <c r="N35" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4625,16 +4625,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="M36" t="n">
-        <v>2.95</v>
+        <v>3.27</v>
       </c>
       <c r="N36" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,16 +4744,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4939,17 +4939,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.96</v>
+        <v>2.55</v>
       </c>
       <c r="M39" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N39" t="n">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="M40" t="n">
-        <v>3.37</v>
+        <v>2.95</v>
       </c>
       <c r="N40" t="n">
-        <v>2.66</v>
+        <v>3.05</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,17 +5296,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.91</v>
+        <v>2.24</v>
       </c>
       <c r="M42" t="n">
-        <v>3.2</v>
+        <v>3.37</v>
       </c>
       <c r="N42" t="n">
-        <v>3.75</v>
+        <v>2.66</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.34</v>
+        <v>3.35</v>
       </c>
       <c r="M43" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N43" t="n">
-        <v>3.05</v>
+        <v>2.08</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="M45" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N45" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M46" t="n">
         <v>3.2</v>
       </c>
-      <c r="M46" t="n">
-        <v>3.4</v>
-      </c>
       <c r="N46" t="n">
-        <v>2.12</v>
+        <v>3.75</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.55</v>
+        <v>1.96</v>
       </c>
       <c r="M47" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N47" t="n">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.21</v>
+        <v>2.56</v>
       </c>
       <c r="M51" t="n">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="N51" t="n">
-        <v>3.16</v>
+        <v>2.4</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.35</v>
+        <v>2.01</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.15</v>
+        <v>1.97</v>
       </c>
       <c r="M52" t="n">
-        <v>3.45</v>
+        <v>3.01</v>
       </c>
       <c r="N52" t="n">
-        <v>2.12</v>
+        <v>3.57</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="M53" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="N53" t="n">
-        <v>2.65</v>
+        <v>3.08</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.97</v>
+        <v>2.21</v>
       </c>
       <c r="M59" t="n">
-        <v>3.01</v>
+        <v>2.84</v>
       </c>
       <c r="N59" t="n">
-        <v>3.57</v>
+        <v>3.16</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="M64" t="n">
-        <v>3.12</v>
+        <v>3.38</v>
       </c>
       <c r="N64" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,14 +8156,14 @@
         </is>
       </c>
       <c r="L65" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M65" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N65" t="n">
         <v>2.59</v>
       </c>
-      <c r="M65" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="N65" t="n">
-        <v>2.53</v>
-      </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.66</v>
+        <v>3.73</v>
       </c>
       <c r="M66" t="n">
-        <v>3.52</v>
+        <v>3.07</v>
       </c>
       <c r="N66" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.22</v>
+        <v>3.65</v>
       </c>
       <c r="M70" t="n">
-        <v>3.56</v>
+        <v>3.29</v>
       </c>
       <c r="N70" t="n">
-        <v>2.95</v>
+        <v>2.03</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.77</v>
+        <v>1.39</v>
       </c>
       <c r="M75" t="n">
-        <v>3.05</v>
+        <v>4.75</v>
       </c>
       <c r="N75" t="n">
-        <v>2.32</v>
+        <v>7.3</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.39</v>
+        <v>2.77</v>
       </c>
       <c r="M76" t="n">
-        <v>4.75</v>
+        <v>3.05</v>
       </c>
       <c r="N76" t="n">
-        <v>7.3</v>
+        <v>2.32</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AB76" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.85</v>
+        <v>3.3</v>
       </c>
       <c r="M34" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="N34" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4506,10 +4506,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.3</v>
+        <v>1.64</v>
       </c>
       <c r="M35" t="n">
-        <v>2.75</v>
+        <v>3.27</v>
       </c>
       <c r="N35" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4625,16 +4625,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="M36" t="n">
-        <v>3.27</v>
+        <v>2.95</v>
       </c>
       <c r="N36" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,16 +4744,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.41</v>
+        <v>3.2</v>
       </c>
       <c r="M38" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="N38" t="n">
-        <v>7</v>
+        <v>2.12</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.55</v>
+        <v>1.96</v>
       </c>
       <c r="M39" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.34</v>
+        <v>1.91</v>
       </c>
       <c r="M40" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="N40" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,17 +5296,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="M42" t="n">
-        <v>3.37</v>
+        <v>2.85</v>
       </c>
       <c r="N42" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5534,17 +5534,17 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.29</v>
+        <v>1.41</v>
       </c>
       <c r="M44" t="n">
-        <v>2.85</v>
+        <v>4.05</v>
       </c>
       <c r="N44" t="n">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="M45" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N45" t="n">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.91</v>
+        <v>2.34</v>
       </c>
       <c r="M46" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="N46" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.96</v>
+        <v>3.35</v>
       </c>
       <c r="M47" t="n">
         <v>3.1</v>
       </c>
       <c r="N47" t="n">
-        <v>3.7</v>
+        <v>2.08</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.97</v>
+        <v>3.39</v>
       </c>
       <c r="M52" t="n">
-        <v>3.01</v>
+        <v>3.23</v>
       </c>
       <c r="N52" t="n">
-        <v>3.57</v>
+        <v>1.94</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.13</v>
+        <v>3.15</v>
       </c>
       <c r="M53" t="n">
-        <v>3.08</v>
+        <v>3.45</v>
       </c>
       <c r="N53" t="n">
-        <v>3.08</v>
+        <v>2.12</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="M54" t="n">
-        <v>3.25</v>
+        <v>3.01</v>
       </c>
       <c r="N54" t="n">
-        <v>2.65</v>
+        <v>3.57</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.21</v>
+        <v>2.56</v>
       </c>
       <c r="M59" t="n">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="N59" t="n">
-        <v>3.16</v>
+        <v>2.4</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.35</v>
+        <v>2.01</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="M61" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N61" t="n">
-        <v>2.12</v>
+        <v>2.65</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>4.1</v>
+        <v>2.21</v>
       </c>
       <c r="M63" t="n">
-        <v>3.45</v>
+        <v>2.84</v>
       </c>
       <c r="N63" t="n">
-        <v>1.86</v>
+        <v>3.16</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.91</v>
+        <v>1.52</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,14 +8037,14 @@
         </is>
       </c>
       <c r="L64" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M64" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N64" t="n">
         <v>2.59</v>
       </c>
-      <c r="M64" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="N64" t="n">
-        <v>2.53</v>
-      </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="M65" t="n">
-        <v>3.12</v>
+        <v>3.38</v>
       </c>
       <c r="N65" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.65</v>
+        <v>2.22</v>
       </c>
       <c r="M70" t="n">
-        <v>3.29</v>
+        <v>3.56</v>
       </c>
       <c r="N70" t="n">
-        <v>2.03</v>
+        <v>2.95</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="M73" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="N73" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.68</v>
+        <v>1.39</v>
       </c>
       <c r="M74" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="N74" t="n">
-        <v>4.7</v>
+        <v>7.3</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.39</v>
+        <v>1.85</v>
       </c>
       <c r="M75" t="n">
-        <v>4.75</v>
+        <v>3.29</v>
       </c>
       <c r="N75" t="n">
-        <v>7.3</v>
+        <v>4.4</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.92</v>
+        <v>3.35</v>
       </c>
       <c r="M32" t="n">
-        <v>3.53</v>
+        <v>3.67</v>
       </c>
       <c r="N32" t="n">
-        <v>3.76</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4506,10 +4506,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="M35" t="n">
-        <v>3.27</v>
+        <v>2.95</v>
       </c>
       <c r="N35" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4625,16 +4625,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="M36" t="n">
-        <v>2.95</v>
+        <v>3.27</v>
       </c>
       <c r="N36" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,16 +4744,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4863,10 +4863,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="M38" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N38" t="n">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.96</v>
+        <v>2.29</v>
       </c>
       <c r="M39" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="N39" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.91</v>
+        <v>3.2</v>
       </c>
       <c r="M40" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N40" t="n">
-        <v>3.75</v>
+        <v>2.12</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.24</v>
+        <v>1.41</v>
       </c>
       <c r="M41" t="n">
-        <v>3.37</v>
+        <v>4.05</v>
       </c>
       <c r="N41" t="n">
-        <v>2.66</v>
+        <v>7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="M42" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N42" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5534,17 +5534,17 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.41</v>
+        <v>1.91</v>
       </c>
       <c r="M44" t="n">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="N44" t="n">
-        <v>7</v>
+        <v>3.75</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5772,17 +5772,17 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="M46" t="n">
-        <v>2.95</v>
+        <v>3.37</v>
       </c>
       <c r="N46" t="n">
-        <v>3.05</v>
+        <v>2.66</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.35</v>
+        <v>1.96</v>
       </c>
       <c r="M47" t="n">
         <v>3.1</v>
       </c>
       <c r="N47" t="n">
-        <v>2.08</v>
+        <v>3.7</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.97</v>
+        <v>2.31</v>
       </c>
       <c r="M54" t="n">
-        <v>3.01</v>
+        <v>3.3</v>
       </c>
       <c r="N54" t="n">
-        <v>3.57</v>
+        <v>2.9</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.56</v>
+        <v>3.39</v>
       </c>
       <c r="M59" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="N59" t="n">
-        <v>2.4</v>
+        <v>1.94</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>4.1</v>
+        <v>2.21</v>
       </c>
       <c r="M60" t="n">
-        <v>3.45</v>
+        <v>2.84</v>
       </c>
       <c r="N60" t="n">
-        <v>1.86</v>
+        <v>3.16</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.91</v>
+        <v>1.52</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="M61" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N61" t="n">
-        <v>2.65</v>
+        <v>1.86</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="M62" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>3.08</v>
+        <v>2.65</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.21</v>
+        <v>3.15</v>
       </c>
       <c r="M63" t="n">
-        <v>2.84</v>
+        <v>3.45</v>
       </c>
       <c r="N63" t="n">
-        <v>3.16</v>
+        <v>2.12</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="M64" t="n">
-        <v>3.12</v>
+        <v>3.38</v>
       </c>
       <c r="N64" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,14 +8156,14 @@
         </is>
       </c>
       <c r="L65" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M65" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N65" t="n">
         <v>2.59</v>
       </c>
-      <c r="M65" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="N65" t="n">
-        <v>2.53</v>
-      </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.22</v>
+        <v>3.65</v>
       </c>
       <c r="M70" t="n">
-        <v>3.56</v>
+        <v>3.29</v>
       </c>
       <c r="N70" t="n">
-        <v>2.95</v>
+        <v>2.03</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.66</v>
+        <v>2.22</v>
       </c>
       <c r="M71" t="n">
-        <v>3.52</v>
+        <v>3.56</v>
       </c>
       <c r="N71" t="n">
-        <v>4.3</v>
+        <v>2.95</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.82</v>
+        <v>2.35</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.39</v>
+        <v>1.85</v>
       </c>
       <c r="M74" t="n">
-        <v>4.75</v>
+        <v>3.29</v>
       </c>
       <c r="N74" t="n">
-        <v>7.3</v>
+        <v>4.4</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.85</v>
+        <v>1.39</v>
       </c>
       <c r="M75" t="n">
-        <v>3.29</v>
+        <v>4.75</v>
       </c>
       <c r="N75" t="n">
-        <v>4.4</v>
+        <v>7.3</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.35</v>
+        <v>1.92</v>
       </c>
       <c r="M32" t="n">
-        <v>3.67</v>
+        <v>3.53</v>
       </c>
       <c r="N32" t="n">
-        <v>2</v>
+        <v>3.76</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.92</v>
+        <v>3.35</v>
       </c>
       <c r="M33" t="n">
-        <v>3.53</v>
+        <v>3.67</v>
       </c>
       <c r="N33" t="n">
-        <v>3.76</v>
+        <v>2</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="M35" t="n">
-        <v>2.95</v>
+        <v>3.27</v>
       </c>
       <c r="N35" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4625,16 +4625,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="M36" t="n">
-        <v>3.27</v>
+        <v>2.95</v>
       </c>
       <c r="N36" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,16 +4744,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.55</v>
+        <v>2.24</v>
       </c>
       <c r="M38" t="n">
-        <v>2.95</v>
+        <v>3.37</v>
       </c>
       <c r="N38" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.29</v>
+        <v>3.2</v>
       </c>
       <c r="M39" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>3.2</v>
+        <v>2.12</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.2</v>
+        <v>1.96</v>
       </c>
       <c r="M40" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N40" t="n">
-        <v>2.12</v>
+        <v>3.7</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.41</v>
+        <v>1.91</v>
       </c>
       <c r="M41" t="n">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="N41" t="n">
-        <v>7</v>
+        <v>3.75</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5415,17 +5415,17 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.35</v>
+        <v>2.29</v>
       </c>
       <c r="M43" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="N43" t="n">
-        <v>2.08</v>
+        <v>3.2</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.91</v>
+        <v>3.35</v>
       </c>
       <c r="M44" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
-        <v>3.75</v>
+        <v>2.08</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5772,17 +5772,17 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.24</v>
+        <v>2.55</v>
       </c>
       <c r="M46" t="n">
-        <v>3.37</v>
+        <v>2.95</v>
       </c>
       <c r="N46" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.96</v>
+        <v>1.41</v>
       </c>
       <c r="M47" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="N47" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.56</v>
+        <v>2.13</v>
       </c>
       <c r="M49" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="N49" t="n">
-        <v>2.4</v>
+        <v>3.08</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.97</v>
+        <v>2.56</v>
       </c>
       <c r="M51" t="n">
-        <v>3.01</v>
+        <v>3.2</v>
       </c>
       <c r="N51" t="n">
-        <v>3.57</v>
+        <v>2.4</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="M58" t="n">
-        <v>3.08</v>
+        <v>2.84</v>
       </c>
       <c r="N58" t="n">
-        <v>3.08</v>
+        <v>3.16</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.94</v>
+        <v>2.35</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.76</v>
+        <v>1.52</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.39</v>
+        <v>2.3</v>
       </c>
       <c r="M59" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="N59" t="n">
-        <v>1.94</v>
+        <v>2.65</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.21</v>
+        <v>3.15</v>
       </c>
       <c r="M60" t="n">
-        <v>2.84</v>
+        <v>3.45</v>
       </c>
       <c r="N60" t="n">
-        <v>3.16</v>
+        <v>2.12</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>4.1</v>
+        <v>2.31</v>
       </c>
       <c r="M61" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N61" t="n">
-        <v>1.86</v>
+        <v>2.9</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.3</v>
+        <v>3.39</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="N62" t="n">
-        <v>2.65</v>
+        <v>1.94</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="M63" t="n">
         <v>3.45</v>
       </c>
       <c r="N63" t="n">
-        <v>2.12</v>
+        <v>1.86</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.73</v>
+        <v>2.22</v>
       </c>
       <c r="M67" t="n">
-        <v>3.07</v>
+        <v>3.56</v>
       </c>
       <c r="N67" t="n">
-        <v>2.1</v>
+        <v>2.95</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.6</v>
+        <v>2.35</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.66</v>
+        <v>3.73</v>
       </c>
       <c r="M68" t="n">
-        <v>3.52</v>
+        <v>3.07</v>
       </c>
       <c r="N68" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.22</v>
+        <v>1.66</v>
       </c>
       <c r="M71" t="n">
-        <v>3.56</v>
+        <v>3.52</v>
       </c>
       <c r="N71" t="n">
-        <v>2.95</v>
+        <v>4.3</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.35</v>
+        <v>1.82</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.85</v>
+        <v>1.39</v>
       </c>
       <c r="M74" t="n">
-        <v>3.29</v>
+        <v>4.75</v>
       </c>
       <c r="N74" t="n">
-        <v>4.4</v>
+        <v>7.3</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.39</v>
+        <v>2.77</v>
       </c>
       <c r="M75" t="n">
-        <v>4.75</v>
+        <v>3.05</v>
       </c>
       <c r="N75" t="n">
-        <v>7.3</v>
+        <v>2.32</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.77</v>
+        <v>1.85</v>
       </c>
       <c r="M76" t="n">
-        <v>3.05</v>
+        <v>3.29</v>
       </c>
       <c r="N76" t="n">
-        <v>2.32</v>
+        <v>4.4</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI80"/>
+  <dimension ref="A1:AI83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="M2" t="n">
-        <v>3.81</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46052.125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -787,64 +787,64 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46052.22916666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46052.22916666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2257,10 +2257,10 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46052.47916666666</v>
+        <v>46052.45833333334</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="N16" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46052.5</v>
+        <v>46052.47916666666</v>
       </c>
     </row>
     <row r="17">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46052.52083333334</v>
+        <v>46052.5</v>
       </c>
     </row>
     <row r="21">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46052.53472222222</v>
+        <v>46052.5</v>
       </c>
     </row>
     <row r="22">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46052.5625</v>
+        <v>46052.5</v>
       </c>
     </row>
     <row r="23">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46052.58333333334</v>
+        <v>46052.52083333334</v>
       </c>
     </row>
     <row r="24">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46052.58333333334</v>
+        <v>46052.53472222222</v>
       </c>
     </row>
     <row r="25">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46052.58333333334</v>
+        <v>46052.5625</v>
       </c>
     </row>
     <row r="26">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="M29" t="n">
-        <v>3.65</v>
+        <v>3.19</v>
       </c>
       <c r="N29" t="n">
-        <v>3.4</v>
+        <v>2.91</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.13</v>
+        <v>1.87</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>46052.59375</v>
+        <v>46052.58333333334</v>
       </c>
     </row>
     <row r="30">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4060,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46052.60416666666</v>
+        <v>46052.58333333334</v>
       </c>
     </row>
     <row r="31">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4179,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>46052.60416666666</v>
+        <v>46052.58333333334</v>
       </c>
     </row>
     <row r="32">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="M32" t="n">
-        <v>3.53</v>
+        <v>3.65</v>
       </c>
       <c r="N32" t="n">
-        <v>3.76</v>
+        <v>3.4</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4277,7 +4277,7 @@
         <v>1.7</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
-        <v>46052.60416666666</v>
+        <v>46052.59375</v>
       </c>
     </row>
     <row r="33">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.35</v>
+        <v>1.92</v>
       </c>
       <c r="M33" t="n">
-        <v>3.67</v>
+        <v>3.53</v>
       </c>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>3.76</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4426,12 +4426,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
-        <v>46052.625</v>
+        <v>46052.60416666666</v>
       </c>
     </row>
     <row r="35">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4655,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
-        <v>46052.625</v>
+        <v>46052.60416666666</v>
       </c>
     </row>
     <row r="36">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,10 +4744,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
-        <v>46052.625</v>
+        <v>46052.60416666666</v>
       </c>
     </row>
     <row r="37">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.3</v>
+        <v>1.85</v>
       </c>
       <c r="M37" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="N37" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4863,10 +4863,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -4902,12 +4902,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.24</v>
+        <v>1.64</v>
       </c>
       <c r="M38" t="n">
-        <v>3.37</v>
+        <v>3.27</v>
       </c>
       <c r="N38" t="n">
-        <v>2.66</v>
+        <v>4.9</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
-        <v>46052.64583333334</v>
+        <v>46052.625</v>
       </c>
     </row>
     <row r="39">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5131,7 +5131,7 @@
         <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
-        <v>46052.64583333334</v>
+        <v>46052.625</v>
       </c>
     </row>
     <row r="40">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.96</v>
+        <v>3.3</v>
       </c>
       <c r="M40" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="N40" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5220,10 +5220,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5250,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
-        <v>46052.64583333334</v>
+        <v>46052.625</v>
       </c>
     </row>
     <row r="41">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.91</v>
+        <v>3.2</v>
       </c>
       <c r="M41" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N41" t="n">
-        <v>3.75</v>
+        <v>2.12</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5415,17 +5415,17 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6092,12 +6092,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -6202,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="AI48" s="3" t="n">
-        <v>46052.65625</v>
+        <v>46052.64583333334</v>
       </c>
     </row>
     <row r="49">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
       <c r="M49" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="N49" t="n">
-        <v>3.08</v>
+        <v>3.7</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="AI49" s="3" t="n">
-        <v>46052.66666666666</v>
+        <v>46052.64583333334</v>
       </c>
     </row>
     <row r="50">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6440,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="AI50" s="3" t="n">
-        <v>46052.66666666666</v>
+        <v>46052.64583333334</v>
       </c>
     </row>
     <row r="51">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>0</v>
       </c>
       <c r="AI51" s="3" t="n">
-        <v>46052.66666666666</v>
+        <v>46052.65625</v>
       </c>
     </row>
     <row r="52">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="M59" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N59" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.31</v>
+        <v>4.1</v>
       </c>
       <c r="M61" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N61" t="n">
-        <v>2.9</v>
+        <v>1.86</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.59</v>
+        <v>1.97</v>
       </c>
       <c r="M64" t="n">
-        <v>3.38</v>
+        <v>3.01</v>
       </c>
       <c r="N64" t="n">
-        <v>2.53</v>
+        <v>3.57</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8106,7 +8106,7 @@
         <v>0</v>
       </c>
       <c r="AI64" s="3" t="n">
-        <v>46052.67708333334</v>
+        <v>46052.66666666666</v>
       </c>
     </row>
     <row r="65">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="AI65" s="3" t="n">
-        <v>46052.67708333334</v>
+        <v>46052.66666666666</v>
       </c>
     </row>
     <row r="66">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8344,7 +8344,7 @@
         <v>0</v>
       </c>
       <c r="AI66" s="3" t="n">
-        <v>46052.6875</v>
+        <v>46052.66666666666</v>
       </c>
     </row>
     <row r="67">
@@ -8353,12 +8353,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="M67" t="n">
-        <v>3.56</v>
+        <v>3.12</v>
       </c>
       <c r="N67" t="n">
-        <v>2.95</v>
+        <v>2.59</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AB67" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8463,7 +8463,7 @@
         <v>0</v>
       </c>
       <c r="AI67" s="3" t="n">
-        <v>46052.6875</v>
+        <v>46052.67708333334</v>
       </c>
     </row>
     <row r="68">
@@ -8472,12 +8472,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.73</v>
+        <v>2.59</v>
       </c>
       <c r="M68" t="n">
-        <v>3.07</v>
+        <v>3.38</v>
       </c>
       <c r="N68" t="n">
-        <v>2.1</v>
+        <v>2.53</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8582,7 +8582,7 @@
         <v>0</v>
       </c>
       <c r="AI68" s="3" t="n">
-        <v>46052.6875</v>
+        <v>46052.67708333334</v>
       </c>
     </row>
     <row r="69">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9067,12 +9067,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.68</v>
+        <v>2.22</v>
       </c>
       <c r="M73" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="N73" t="n">
-        <v>4.7</v>
+        <v>2.95</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9177,7 +9177,7 @@
         <v>0</v>
       </c>
       <c r="AI73" s="3" t="n">
-        <v>46052.69791666666</v>
+        <v>46052.6875</v>
       </c>
     </row>
     <row r="74">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.39</v>
+        <v>3.73</v>
       </c>
       <c r="M74" t="n">
-        <v>4.75</v>
+        <v>3.07</v>
       </c>
       <c r="N74" t="n">
-        <v>7.3</v>
+        <v>2.1</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9296,7 +9296,7 @@
         <v>0</v>
       </c>
       <c r="AI74" s="3" t="n">
-        <v>46052.69791666666</v>
+        <v>46052.6875</v>
       </c>
     </row>
     <row r="75">
@@ -9305,12 +9305,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.77</v>
+        <v>3.65</v>
       </c>
       <c r="M75" t="n">
-        <v>3.05</v>
+        <v>3.29</v>
       </c>
       <c r="N75" t="n">
-        <v>2.32</v>
+        <v>2.03</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9415,7 +9415,7 @@
         <v>0</v>
       </c>
       <c r="AI75" s="3" t="n">
-        <v>46052.69791666666</v>
+        <v>46052.6875</v>
       </c>
     </row>
     <row r="76">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.85</v>
+        <v>1.39</v>
       </c>
       <c r="M76" t="n">
-        <v>3.29</v>
+        <v>4.75</v>
       </c>
       <c r="N76" t="n">
-        <v>4.4</v>
+        <v>7.3</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9543,12 +9543,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.99</v>
+        <v>1.68</v>
       </c>
       <c r="M77" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N77" t="n">
-        <v>3.77</v>
+        <v>4.7</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9653,7 +9653,7 @@
         <v>0</v>
       </c>
       <c r="AI77" s="3" t="n">
-        <v>46052.70833333334</v>
+        <v>46052.69791666666</v>
       </c>
     </row>
     <row r="78">
@@ -9662,12 +9662,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9772,7 +9772,7 @@
         <v>0</v>
       </c>
       <c r="AI78" s="3" t="n">
-        <v>46052.70833333334</v>
+        <v>46052.69791666666</v>
       </c>
     </row>
     <row r="79">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="AI79" s="3" t="n">
-        <v>46052.73958333334</v>
+        <v>46052.69791666666</v>
       </c>
     </row>
     <row r="80">
@@ -9900,116 +9900,473 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RCD Espanyol</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Deportivo Alavés</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI80" s="3" t="n">
+        <v>46052.70833333334</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Bristol City</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Derby County</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="M81" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N81" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI81" s="3" t="n">
+        <v>46052.70833333334</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Vitória Guimarães</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Moreirense FC</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI82" s="3" t="n">
+        <v>46052.73958333334</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Chile Primera División</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>Universidad Chile</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Audax Italiano</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" t="inlineStr">
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" t="n">
-        <v>0</v>
-      </c>
-      <c r="S80" t="n">
-        <v>0</v>
-      </c>
-      <c r="T80" t="n">
-        <v>0</v>
-      </c>
-      <c r="U80" t="n">
-        <v>0</v>
-      </c>
-      <c r="V80" t="n">
-        <v>0</v>
-      </c>
-      <c r="W80" t="n">
-        <v>0</v>
-      </c>
-      <c r="X80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA80" t="n">
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0</v>
+      </c>
+      <c r="X83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA83" t="n">
         <v>1.65</v>
       </c>
-      <c r="AB80" t="n">
+      <c r="AB83" t="n">
         <v>2.2</v>
       </c>
-      <c r="AC80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI80" s="3" t="n">
+      <c r="AC83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI83" s="3" t="n">
         <v>46052.83333333334</v>
       </c>
     </row>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O3" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.46</v>
+        <v>2.38</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U3" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>6.65</v>
+        <v>6.1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.32</v>
+        <v>2.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46052.22916666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3.46</v>
       </c>
-      <c r="N4" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="O4" t="n">
-        <v>4</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.38</v>
-      </c>
       <c r="R4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V4" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.35</v>
       </c>
-      <c r="S4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V4" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH4" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46052.22916666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.7</v>
+        <v>2.16</v>
       </c>
       <c r="M27" t="n">
-        <v>3.45</v>
+        <v>3.19</v>
       </c>
       <c r="N27" t="n">
-        <v>1.7</v>
+        <v>2.91</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,16 +4631,16 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.64</v>
+        <v>3.3</v>
       </c>
       <c r="M38" t="n">
-        <v>3.27</v>
+        <v>2.75</v>
       </c>
       <c r="N38" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4982,16 +4982,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.3</v>
+        <v>1.64</v>
       </c>
       <c r="M40" t="n">
-        <v>2.75</v>
+        <v>3.27</v>
       </c>
       <c r="N40" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5220,16 +5220,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.2</v>
+        <v>1.96</v>
       </c>
       <c r="M41" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>2.12</v>
+        <v>3.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.29</v>
+        <v>3.35</v>
       </c>
       <c r="M43" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="N43" t="n">
-        <v>3.2</v>
+        <v>2.08</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5653,17 +5653,17 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.41</v>
+        <v>3.2</v>
       </c>
       <c r="M47" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="N47" t="n">
-        <v>7</v>
+        <v>2.12</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,17 +6129,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.96</v>
+        <v>1.41</v>
       </c>
       <c r="M49" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="N49" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="M50" t="n">
-        <v>3.37</v>
+        <v>2.85</v>
       </c>
       <c r="N50" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.39</v>
+        <v>4.1</v>
       </c>
       <c r="M57" t="n">
-        <v>3.23</v>
+        <v>3.45</v>
       </c>
       <c r="N57" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.31</v>
+        <v>2.56</v>
       </c>
       <c r="M59" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N59" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.15</v>
+        <v>3.39</v>
       </c>
       <c r="M60" t="n">
-        <v>3.45</v>
+        <v>3.23</v>
       </c>
       <c r="N60" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="M64" t="n">
-        <v>3.01</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>3.57</v>
+        <v>2.65</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,55 +9227,55 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.73</v>
+        <v>3.65</v>
       </c>
       <c r="M74" t="n">
-        <v>3.07</v>
+        <v>3.29</v>
       </c>
       <c r="N74" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA74" t="n">
         <v>2.1</v>
       </c>
-      <c r="O74" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" t="n">
-        <v>0</v>
-      </c>
-      <c r="T74" t="n">
-        <v>0</v>
-      </c>
-      <c r="U74" t="n">
-        <v>0</v>
-      </c>
-      <c r="V74" t="n">
-        <v>0</v>
-      </c>
-      <c r="W74" t="n">
-        <v>0</v>
-      </c>
-      <c r="X74" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y74" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA74" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AB74" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.65</v>
+        <v>2.22</v>
       </c>
       <c r="M75" t="n">
-        <v>3.29</v>
+        <v>3.56</v>
       </c>
       <c r="N75" t="n">
-        <v>2.03</v>
+        <v>2.95</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="M77" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="N77" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="M78" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="N78" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -793,7 +793,7 @@
         <v>2.11</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R3" t="n">
         <v>1.35</v>
@@ -805,7 +805,7 @@
         <v>2.6</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V3" t="n">
         <v>6.1</v>
@@ -814,13 +814,13 @@
         <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
         <v>1.18</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.42</v>
+        <v>3.63</v>
       </c>
       <c r="AA3" t="n">
         <v>1.8</v>
@@ -841,7 +841,7 @@
         <v>1.97</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.22</v>
+        <v>1.8</v>
       </c>
       <c r="AH3" t="n">
         <v>1.18</v>
@@ -918,13 +918,13 @@
         <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>2.94</v>
+        <v>2.56</v>
       </c>
       <c r="T4" t="n">
         <v>2.75</v>
       </c>
       <c r="U4" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V4" t="n">
         <v>6.65</v>
@@ -942,7 +942,7 @@
         <v>3.14</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AB4" t="n">
         <v>1.78</v>
@@ -954,16 +954,16 @@
         <v>1.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AF4" t="n">
         <v>2.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46052.22916666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2096,64 +2096,64 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46052.45138888889</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.9</v>
+        <v>1.14</v>
       </c>
       <c r="M22" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="N22" t="n">
-        <v>3.8</v>
+        <v>8.1</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46052.5</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.35</v>
+        <v>1.92</v>
       </c>
       <c r="M35" t="n">
-        <v>3.67</v>
+        <v>3.53</v>
       </c>
       <c r="N35" t="n">
-        <v>2</v>
+        <v>3.76</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,16 +4631,16 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.92</v>
+        <v>3.35</v>
       </c>
       <c r="M36" t="n">
-        <v>3.53</v>
+        <v>3.67</v>
       </c>
       <c r="N36" t="n">
-        <v>3.76</v>
+        <v>2</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,16 +4750,16 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.85</v>
+        <v>3.3</v>
       </c>
       <c r="M37" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="N37" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4863,10 +4863,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.3</v>
+        <v>1.64</v>
       </c>
       <c r="M38" t="n">
-        <v>2.75</v>
+        <v>3.27</v>
       </c>
       <c r="N38" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4982,16 +4982,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5101,10 +5101,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,17 +5296,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.35</v>
+        <v>1.96</v>
       </c>
       <c r="M43" t="n">
         <v>3.1</v>
       </c>
       <c r="N43" t="n">
-        <v>2.08</v>
+        <v>3.7</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5653,17 +5653,17 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.34</v>
+        <v>1.41</v>
       </c>
       <c r="M45" t="n">
-        <v>2.95</v>
+        <v>4.05</v>
       </c>
       <c r="N45" t="n">
-        <v>3.05</v>
+        <v>7</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.2</v>
+        <v>2.34</v>
       </c>
       <c r="M47" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N47" t="n">
-        <v>2.12</v>
+        <v>3.05</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.24</v>
+        <v>3.2</v>
       </c>
       <c r="M48" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="N48" t="n">
-        <v>2.66</v>
+        <v>2.12</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.41</v>
+        <v>3.35</v>
       </c>
       <c r="M49" t="n">
-        <v>4.05</v>
+        <v>3.1</v>
       </c>
       <c r="N49" t="n">
-        <v>7</v>
+        <v>2.08</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="M50" t="n">
-        <v>2.85</v>
+        <v>3.37</v>
       </c>
       <c r="N50" t="n">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.31</v>
+        <v>1.97</v>
       </c>
       <c r="M52" t="n">
-        <v>3.3</v>
+        <v>3.01</v>
       </c>
       <c r="N52" t="n">
-        <v>2.9</v>
+        <v>3.57</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>4.1</v>
+        <v>2.56</v>
       </c>
       <c r="M57" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N57" t="n">
-        <v>1.86</v>
+        <v>2.4</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="M58" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N58" t="n">
-        <v>2.12</v>
+        <v>2.65</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.56</v>
+        <v>2.21</v>
       </c>
       <c r="M59" t="n">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="N59" t="n">
-        <v>2.4</v>
+        <v>3.16</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.01</v>
+        <v>2.35</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.39</v>
+        <v>2.77</v>
       </c>
       <c r="M76" t="n">
-        <v>4.75</v>
+        <v>3.05</v>
       </c>
       <c r="N76" t="n">
-        <v>7.3</v>
+        <v>2.32</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AB76" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="M77" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="N77" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="M78" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="N78" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.77</v>
+        <v>1.39</v>
       </c>
       <c r="M79" t="n">
-        <v>3.05</v>
+        <v>4.75</v>
       </c>
       <c r="N79" t="n">
-        <v>2.32</v>
+        <v>7.3</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -665,7 +665,7 @@
         <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O2" t="n">
         <v>4</v>
@@ -701,22 +701,22 @@
         <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
         <v>3.18</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AF2" t="n">
         <v>2</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="M5" t="n">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="N5" t="n">
-        <v>3.26</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46052.23263888889</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2096,28 +2096,28 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="Q14" t="n">
         <v>5.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="S14" t="n">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
         <v>2.6</v>
       </c>
       <c r="U14" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="V14" t="n">
-        <v>6.35</v>
+        <v>6</v>
       </c>
       <c r="W14" t="n">
         <v>1.06</v>
@@ -2129,31 +2129,31 @@
         <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AG14" t="n">
         <v>1.18</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46052.45138888889</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3286,64 +3286,64 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46052.53472222222</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.7</v>
+        <v>2.16</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>3.19</v>
       </c>
       <c r="N26" t="n">
-        <v>1.7</v>
+        <v>2.91</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.16</v>
+        <v>4.7</v>
       </c>
       <c r="M27" t="n">
-        <v>3.19</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>2.91</v>
+        <v>1.7</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>16.53</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46052.58333333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.35</v>
+        <v>9.85</v>
       </c>
       <c r="M36" t="n">
-        <v>3.67</v>
+        <v>6.65</v>
       </c>
       <c r="N36" t="n">
-        <v>2</v>
+        <v>1.17</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>7.39</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AE36" t="n">
         <v>1.58</v>
       </c>
-      <c r="AB36" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46052.60416666666</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.3</v>
+        <v>1.85</v>
       </c>
       <c r="M37" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="N37" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4863,10 +4863,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.85</v>
+        <v>3.3</v>
       </c>
       <c r="M39" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="N39" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5101,10 +5101,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,17 +5296,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.91</v>
+        <v>3.2</v>
       </c>
       <c r="M42" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>3.75</v>
+        <v>2.12</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.96</v>
+        <v>2.29</v>
       </c>
       <c r="M43" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="N43" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="M44" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N44" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.41</v>
+        <v>2.34</v>
       </c>
       <c r="M45" t="n">
-        <v>4.05</v>
+        <v>2.95</v>
       </c>
       <c r="N45" t="n">
-        <v>7</v>
+        <v>3.05</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.55</v>
+        <v>1.41</v>
       </c>
       <c r="M46" t="n">
-        <v>2.95</v>
+        <v>4.05</v>
       </c>
       <c r="N46" t="n">
-        <v>2.75</v>
+        <v>7</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.34</v>
+        <v>1.96</v>
       </c>
       <c r="M47" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N47" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,17 +6129,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6499,40 +6499,40 @@
         <v>2.75</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA51" t="n">
         <v>2.1</v>
@@ -6541,22 +6541,22 @@
         <v>1.65</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46052.65625</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.39</v>
+        <v>2.31</v>
       </c>
       <c r="M53" t="n">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="N53" t="n">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="M55" t="n">
         <v>3.45</v>
       </c>
       <c r="N55" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.31</v>
+        <v>4.1</v>
       </c>
       <c r="M56" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N56" t="n">
-        <v>2.9</v>
+        <v>1.86</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="M66" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N66" t="n">
-        <v>2.12</v>
+        <v>2.65</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.66</v>
+        <v>2.22</v>
       </c>
       <c r="M73" t="n">
-        <v>3.52</v>
+        <v>3.56</v>
       </c>
       <c r="N73" t="n">
-        <v>4.3</v>
+        <v>2.95</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.82</v>
+        <v>2.35</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.77</v>
+        <v>1.39</v>
       </c>
       <c r="M76" t="n">
-        <v>3.05</v>
+        <v>4.75</v>
       </c>
       <c r="N76" t="n">
-        <v>2.32</v>
+        <v>7.3</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.68</v>
+        <v>2.77</v>
       </c>
       <c r="M77" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="N77" t="n">
-        <v>4.7</v>
+        <v>2.32</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.39</v>
+        <v>1.68</v>
       </c>
       <c r="M79" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="N79" t="n">
-        <v>7.3</v>
+        <v>4.7</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB79" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q3" t="n">
         <v>3.46</v>
       </c>
-      <c r="N3" t="n">
+      <c r="R3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V3" t="n">
+        <v>7</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB3" t="n">
         <v>1.82</v>
       </c>
-      <c r="O3" t="n">
-        <v>4</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2</v>
-      </c>
       <c r="AC3" t="n">
-        <v>2.88</v>
+        <v>3.32</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
         <v>1.69</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46052.22916666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O4" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.46</v>
+        <v>2.41</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="T4" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>6.65</v>
+        <v>6.15</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.32</v>
+        <v>2.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE4" t="n">
         <v>1.69</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.2</v>
+        <v>1.79</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46052.22916666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="M16" t="n">
         <v>4.2</v>
       </c>
       <c r="N16" t="n">
-        <v>4.9</v>
+        <v>5.61</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46052.47916666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46052.5</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46052.5</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.14</v>
+        <v>1.83</v>
       </c>
       <c r="M22" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>8.1</v>
+        <v>3.6</v>
       </c>
       <c r="O22" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>9.5</v>
+        <v>3.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="T22" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="U22" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="V22" t="n">
-        <v>5.05</v>
+        <v>5.6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
         <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.35</v>
+        <v>4.15</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.51</v>
+        <v>1.61</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.46</v>
+        <v>2.23</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AH22" t="n">
-        <v>4.3</v>
+        <v>1.79</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46052.5</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46052.58333333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.7</v>
+        <v>3.76</v>
       </c>
       <c r="M27" t="n">
-        <v>3.45</v>
+        <v>3.57</v>
       </c>
       <c r="N27" t="n">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46052.58333333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>16.53</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46052.58333333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46052.58333333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46052.58333333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.07</v>
+        <v>2.23</v>
       </c>
       <c r="M31" t="n">
-        <v>10</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>16.53</v>
+        <v>3.07</v>
       </c>
       <c r="O31" t="n">
-        <v>1.32</v>
+        <v>2.88</v>
       </c>
       <c r="P31" t="n">
-        <v>3.95</v>
+        <v>2.07</v>
       </c>
       <c r="Q31" t="n">
-        <v>13</v>
+        <v>3.73</v>
       </c>
       <c r="R31" t="n">
-        <v>1.15</v>
+        <v>1.38</v>
       </c>
       <c r="S31" t="n">
-        <v>5.3</v>
+        <v>2.77</v>
       </c>
       <c r="T31" t="n">
-        <v>1.69</v>
+        <v>2.69</v>
       </c>
       <c r="U31" t="n">
-        <v>2.01</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>3.14</v>
+        <v>6.25</v>
       </c>
       <c r="W31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AG31" t="n">
         <v>1.3</v>
       </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AH31" t="n">
-        <v>6.8</v>
+        <v>1.56</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46052.58333333334</v>
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.08</v>
+        <v>1.73</v>
       </c>
       <c r="M32" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N32" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46052.59375</v>
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.35</v>
+        <v>2.5</v>
       </c>
       <c r="M33" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.25</v>
+        <v>2.53</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46052.60416666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46052.60416666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.92</v>
+        <v>9.85</v>
       </c>
       <c r="M35" t="n">
-        <v>3.53</v>
+        <v>6.65</v>
       </c>
       <c r="N35" t="n">
-        <v>3.76</v>
+        <v>1.17</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>7.39</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC35" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB35" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46052.60416666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>9.85</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>7.39</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46052.60416666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="M37" t="n">
-        <v>2.95</v>
+        <v>3.76</v>
       </c>
       <c r="N37" t="n">
-        <v>5</v>
+        <v>6.84</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AF37" t="n">
         <v>1.55</v>
       </c>
-      <c r="Z37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0</v>
-      </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46052.625</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46052.625</v>
@@ -5062,7 +5062,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="M39" t="n">
         <v>2.75</v>
@@ -5071,64 +5071,64 @@
         <v>2.4</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46052.625</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.64</v>
+        <v>2.6</v>
       </c>
       <c r="M40" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>4.9</v>
+        <v>2.25</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46052.625</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,17 +5296,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N42" t="n">
         <v>3.2</v>
       </c>
-      <c r="M42" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N42" t="n">
-        <v>2.12</v>
-      </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.78</v>
+        <v>2.35</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.97</v>
+        <v>1.57</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46052.64583333334</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.29</v>
+        <v>1.91</v>
       </c>
       <c r="M43" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="N43" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46052.64583333334</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.55</v>
+        <v>1.96</v>
       </c>
       <c r="M44" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46052.64583333334</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.34</v>
+        <v>3.35</v>
       </c>
       <c r="M45" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N45" t="n">
-        <v>3.05</v>
+        <v>2.08</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46052.64583333334</v>
@@ -5904,40 +5904,40 @@
         <v>7</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA46" t="n">
         <v>1.9</v>
@@ -5946,22 +5946,22 @@
         <v>1.81</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46052.64583333334</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.96</v>
+        <v>3.2</v>
       </c>
       <c r="M47" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N47" t="n">
-        <v>3.7</v>
+        <v>2.12</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46052.64583333334</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,77 +6129,77 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46052.64583333334</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.35</v>
+        <v>2.34</v>
       </c>
       <c r="M49" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N49" t="n">
-        <v>2.08</v>
+        <v>3.05</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46052.64583333334</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.24</v>
+        <v>2.55</v>
       </c>
       <c r="M50" t="n">
-        <v>3.37</v>
+        <v>2.95</v>
       </c>
       <c r="N50" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46052.64583333334</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,73 +6609,73 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46052.66666666666</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,73 +6728,73 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="M53" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N53" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46052.66666666666</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46052.66666666666</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3.15</v>
+        <v>1.97</v>
       </c>
       <c r="M55" t="n">
-        <v>3.45</v>
+        <v>3.01</v>
       </c>
       <c r="N55" t="n">
-        <v>2.12</v>
+        <v>3.57</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,73 +7085,73 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>4.1</v>
+        <v>2.13</v>
       </c>
       <c r="M56" t="n">
-        <v>3.45</v>
+        <v>3.08</v>
       </c>
       <c r="N56" t="n">
-        <v>1.86</v>
+        <v>3.08</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,73 +7323,73 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,73 +7561,73 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI60" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,73 +7680,73 @@
         </is>
       </c>
       <c r="L61" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M61" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="N61" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O61" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P61" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S61" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V61" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="W61" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X61" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF61" t="n">
         <v>2.21</v>
       </c>
-      <c r="M61" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="N61" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>0</v>
-      </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH61" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AI61" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,73 +7799,73 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.39</v>
+        <v>1.25</v>
       </c>
       <c r="M62" t="n">
-        <v>3.23</v>
+        <v>5.95</v>
       </c>
       <c r="N62" t="n">
-        <v>1.94</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X62" t="n">
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.95</v>
+        <v>1.27</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.75</v>
+        <v>3.14</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AI62" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,73 +7918,73 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.56</v>
+        <v>4.1</v>
       </c>
       <c r="M63" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N63" t="n">
-        <v>2.4</v>
+        <v>1.86</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI63" s="3" t="n">
         <v>46052.66666666666</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,73 +8037,73 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="M64" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>3.08</v>
+        <v>2.65</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI64" s="3" t="n">
         <v>46052.66666666666</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,73 +8156,73 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.97</v>
+        <v>2.56</v>
       </c>
       <c r="M65" t="n">
-        <v>3.01</v>
+        <v>3.2</v>
       </c>
       <c r="N65" t="n">
-        <v>3.57</v>
+        <v>2.4</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI65" s="3" t="n">
         <v>46052.66666666666</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,73 +8275,73 @@
         </is>
       </c>
       <c r="L66" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M66" t="n">
+        <v>4</v>
+      </c>
+      <c r="N66" t="n">
+        <v>5</v>
+      </c>
+      <c r="O66" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="P66" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>5</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S66" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V66" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF66" t="n">
         <v>2.3</v>
       </c>
-      <c r="M66" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N66" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" t="n">
-        <v>0</v>
-      </c>
-      <c r="W66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>0</v>
-      </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AI66" s="3" t="n">
         <v>46052.66666666666</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,73 +8394,73 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="M67" t="n">
-        <v>3.12</v>
+        <v>3.38</v>
       </c>
       <c r="N67" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.87</v>
+        <v>2.29</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI67" s="3" t="n">
         <v>46052.67708333334</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,73 +8513,73 @@
         </is>
       </c>
       <c r="L68" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M68" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N68" t="n">
         <v>2.59</v>
       </c>
-      <c r="M68" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="N68" t="n">
-        <v>2.53</v>
-      </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI68" s="3" t="n">
         <v>46052.67708333334</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,73 +8632,73 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI69" s="3" t="n">
         <v>46052.6875</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,73 +9108,73 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.22</v>
+        <v>1.66</v>
       </c>
       <c r="M73" t="n">
-        <v>3.56</v>
+        <v>3.52</v>
       </c>
       <c r="N73" t="n">
-        <v>2.95</v>
+        <v>4.3</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="AB73" t="n">
-        <v>2.35</v>
+        <v>1.82</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD73" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH73" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI73" s="3" t="n">
         <v>46052.6875</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,73 +9227,73 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.65</v>
+        <v>2.22</v>
       </c>
       <c r="M74" t="n">
-        <v>3.29</v>
+        <v>3.56</v>
       </c>
       <c r="N74" t="n">
-        <v>2.03</v>
+        <v>2.95</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V74" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W74" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG74" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH74" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI74" s="3" t="n">
         <v>46052.6875</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,73 +9465,73 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.39</v>
+        <v>1.68</v>
       </c>
       <c r="M76" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="N76" t="n">
-        <v>7.3</v>
+        <v>4.7</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V76" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W76" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X76" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB76" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD76" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH76" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI76" s="3" t="n">
         <v>46052.69791666666</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,73 +9584,73 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.77</v>
+        <v>1.85</v>
       </c>
       <c r="M77" t="n">
-        <v>3.05</v>
+        <v>3.29</v>
       </c>
       <c r="N77" t="n">
-        <v>2.32</v>
+        <v>4.4</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="W77" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="AB77" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH77" t="n">
         <v>1.81</v>
-      </c>
-      <c r="AC77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH77" t="n">
-        <v>0</v>
       </c>
       <c r="AI77" s="3" t="n">
         <v>46052.69791666666</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,73 +9703,73 @@
         </is>
       </c>
       <c r="L78" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M78" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="N78" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O78" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P78" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="R78" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S78" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V78" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W78" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X78" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE78" t="n">
         <v>1.85</v>
       </c>
-      <c r="M78" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="N78" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" t="n">
-        <v>0</v>
-      </c>
-      <c r="V78" t="n">
-        <v>0</v>
-      </c>
-      <c r="W78" t="n">
-        <v>0</v>
-      </c>
-      <c r="X78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA78" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB78" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="n">
-        <v>0</v>
-      </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG78" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH78" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AI78" s="3" t="n">
         <v>46052.69791666666</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,73 +9822,73 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.68</v>
+        <v>2.77</v>
       </c>
       <c r="M79" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="N79" t="n">
-        <v>4.7</v>
+        <v>2.32</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V79" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="W79" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD79" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG79" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH79" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI79" s="3" t="n">
         <v>46052.69791666666</v>
@@ -9941,73 +9941,73 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W80" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI80" s="3" t="n">
         <v>46052.70833333334</v>
@@ -10060,73 +10060,73 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="M81" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="N81" t="n">
-        <v>3.77</v>
+        <v>3.7</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI81" s="3" t="n">
         <v>46052.70833333334</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46052.5</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46052.5</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46052.5</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46052.5</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>4.6</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="N26" t="n">
-        <v>2.95</v>
+        <v>1.7</v>
       </c>
       <c r="O26" t="n">
-        <v>2.88</v>
+        <v>4.75</v>
       </c>
       <c r="P26" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.65</v>
+        <v>2.34</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S26" t="n">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
       <c r="T26" t="n">
-        <v>3.07</v>
+        <v>2.99</v>
       </c>
       <c r="U26" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V26" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="W26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X26" t="n">
         <v>1.03</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
         <v>1.33</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AB26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF26" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.9</v>
       </c>
       <c r="AG26" t="n">
         <v>1.28</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.56</v>
+        <v>1.15</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46052.58333333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.76</v>
+        <v>2.9</v>
       </c>
       <c r="M27" t="n">
-        <v>3.57</v>
+        <v>3.24</v>
       </c>
       <c r="N27" t="n">
-        <v>1.96</v>
+        <v>2.49</v>
       </c>
       <c r="O27" t="n">
-        <v>4.25</v>
+        <v>3.25</v>
       </c>
       <c r="P27" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.55</v>
+        <v>3.04</v>
       </c>
       <c r="R27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U27" t="n">
         <v>1.36</v>
       </c>
-      <c r="S27" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V27" t="n">
-        <v>6.65</v>
+        <v>7.6</v>
       </c>
       <c r="W27" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="AA27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF27" t="n">
         <v>1.94</v>
       </c>
-      <c r="AB27" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AG27" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46052.58333333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.07</v>
+        <v>2.3</v>
       </c>
       <c r="M28" t="n">
-        <v>10</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>16.53</v>
+        <v>2.95</v>
       </c>
       <c r="O28" t="n">
-        <v>1.32</v>
+        <v>2.88</v>
       </c>
       <c r="P28" t="n">
-        <v>3.95</v>
+        <v>2.09</v>
       </c>
       <c r="Q28" t="n">
-        <v>13</v>
+        <v>3.65</v>
       </c>
       <c r="R28" t="n">
-        <v>1.15</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>5.3</v>
+        <v>2.77</v>
       </c>
       <c r="T28" t="n">
-        <v>1.69</v>
+        <v>3.07</v>
       </c>
       <c r="U28" t="n">
-        <v>2.01</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>3.14</v>
+        <v>7.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>9.300000000000001</v>
+        <v>2.97</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.18</v>
+        <v>2.05</v>
       </c>
       <c r="AB28" t="n">
-        <v>4.2</v>
+        <v>1.73</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.49</v>
+        <v>3.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.27</v>
+        <v>1.21</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="AH28" t="n">
-        <v>6.8</v>
+        <v>1.56</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46052.58333333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.9</v>
+        <v>2.23</v>
       </c>
       <c r="M29" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>2.49</v>
+        <v>3.07</v>
       </c>
       <c r="O29" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="P29" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.04</v>
+        <v>3.73</v>
       </c>
       <c r="R29" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="T29" t="n">
-        <v>3.02</v>
+        <v>2.69</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V29" t="n">
-        <v>7.6</v>
+        <v>6.25</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.54</v>
+        <v>3.05</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46052.58333333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.6</v>
+        <v>3.76</v>
       </c>
       <c r="M30" t="n">
-        <v>3.34</v>
+        <v>3.57</v>
       </c>
       <c r="N30" t="n">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="O30" t="n">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="P30" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="R30" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="T30" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="U30" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>7.6</v>
+        <v>6.65</v>
       </c>
       <c r="W30" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.05</v>
+        <v>3.38</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.66</v>
+        <v>1.94</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.08</v>
+        <v>1.72</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.73</v>
+        <v>2.01</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46052.58333333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.23</v>
+        <v>1.07</v>
       </c>
       <c r="M31" t="n">
-        <v>3.25</v>
+        <v>10</v>
       </c>
       <c r="N31" t="n">
-        <v>3.07</v>
+        <v>16.53</v>
       </c>
       <c r="O31" t="n">
-        <v>2.88</v>
+        <v>1.32</v>
       </c>
       <c r="P31" t="n">
-        <v>2.07</v>
+        <v>3.95</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.73</v>
+        <v>13</v>
       </c>
       <c r="R31" t="n">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="S31" t="n">
-        <v>2.77</v>
+        <v>5.3</v>
       </c>
       <c r="T31" t="n">
-        <v>2.69</v>
+        <v>1.69</v>
       </c>
       <c r="U31" t="n">
-        <v>1.4</v>
+        <v>2.01</v>
       </c>
       <c r="V31" t="n">
-        <v>6.25</v>
+        <v>3.14</v>
       </c>
       <c r="W31" t="n">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="X31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.28</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.91</v>
+        <v>1.18</v>
       </c>
       <c r="AB31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AE31" t="n">
         <v>1.88</v>
       </c>
-      <c r="AC31" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AF31" t="n">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.56</v>
+        <v>6.8</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46052.58333333334</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="M37" t="n">
-        <v>3.76</v>
+        <v>2.8</v>
       </c>
       <c r="N37" t="n">
-        <v>6.84</v>
+        <v>4.5</v>
       </c>
       <c r="O37" t="n">
-        <v>2.11</v>
+        <v>2.92</v>
       </c>
       <c r="P37" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="Q37" t="n">
-        <v>7.5</v>
+        <v>6.26</v>
       </c>
       <c r="R37" t="n">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="S37" t="n">
-        <v>2.44</v>
+        <v>2.04</v>
       </c>
       <c r="T37" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="U37" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="V37" t="n">
-        <v>7.9</v>
+        <v>15</v>
       </c>
       <c r="W37" t="n">
         <v>1.02</v>
       </c>
       <c r="X37" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD37" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="AE37" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AF37" t="n">
         <v>1.42</v>
       </c>
-      <c r="Z37" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AG37" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.38</v>
+        <v>1.77</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46052.625</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="M38" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="N38" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="O38" t="n">
-        <v>2.92</v>
+        <v>3.8</v>
       </c>
       <c r="P38" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.26</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="S38" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="T38" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="U38" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="V38" t="n">
-        <v>15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W38" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.39</v>
+        <v>2.49</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AC38" t="n">
-        <v>7.5</v>
+        <v>4.7</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AE38" t="n">
-        <v>2.64</v>
+        <v>2.09</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.77</v>
+        <v>1.27</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46052.625</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="N39" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T39" t="n">
         <v>3.1</v>
       </c>
-      <c r="M39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="N39" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O39" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U39" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="V39" t="n">
-        <v>9.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="W39" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X39" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.36</v>
+        <v>2.8</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.49</v>
+        <v>2.27</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="AC39" t="n">
-        <v>4.7</v>
+        <v>3.96</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.09</v>
+        <v>2.31</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.27</v>
+        <v>2.38</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46052.625</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,77 +5296,77 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46052.64583333334</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.29</v>
+        <v>3.2</v>
       </c>
       <c r="M42" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>3.2</v>
+        <v>2.12</v>
       </c>
       <c r="O42" t="n">
-        <v>2.62</v>
+        <v>3.86</v>
       </c>
       <c r="P42" t="n">
-        <v>1.86</v>
+        <v>2.13</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.2</v>
+        <v>2.66</v>
       </c>
       <c r="R42" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="S42" t="n">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="T42" t="n">
-        <v>3.25</v>
+        <v>2.56</v>
       </c>
       <c r="U42" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="V42" t="n">
-        <v>8.699999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="W42" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X42" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.62</v>
+        <v>3.58</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.35</v>
+        <v>1.78</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.57</v>
+        <v>1.97</v>
       </c>
       <c r="AC42" t="n">
-        <v>4.32</v>
+        <v>2.94</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.76</v>
+        <v>2.14</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46052.64583333334</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M43" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="N43" t="n">
+        <v>7</v>
+      </c>
+      <c r="O43" t="n">
         <v>1.91</v>
       </c>
-      <c r="M43" t="n">
+      <c r="P43" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>7</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V43" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z43" t="n">
         <v>3.2</v>
       </c>
-      <c r="N43" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O43" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T43" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V43" t="n">
-        <v>8</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AA43" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE43" t="n">
         <v>2.12</v>
       </c>
-      <c r="AB43" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AF43" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.77</v>
+        <v>2.64</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46052.64583333334</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.35</v>
+        <v>1.91</v>
       </c>
       <c r="M45" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N45" t="n">
-        <v>2.08</v>
+        <v>3.75</v>
       </c>
       <c r="O45" t="n">
-        <v>4.27</v>
+        <v>2.49</v>
       </c>
       <c r="P45" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="R45" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="S45" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="T45" t="n">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="U45" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="V45" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W45" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X45" t="n">
         <v>1.03</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AC45" t="n">
-        <v>4.05</v>
+        <v>3.72</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE45" t="n">
         <v>1.92</v>
       </c>
       <c r="AF45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH45" t="n">
         <v>1.77</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46052.64583333334</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.41</v>
+        <v>2.24</v>
       </c>
       <c r="M46" t="n">
-        <v>4.05</v>
+        <v>3.37</v>
       </c>
       <c r="N46" t="n">
-        <v>7</v>
+        <v>2.66</v>
       </c>
       <c r="O46" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="P46" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="Q46" t="n">
-        <v>7</v>
+        <v>3.12</v>
       </c>
       <c r="R46" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="S46" t="n">
-        <v>2.78</v>
+        <v>3.18</v>
       </c>
       <c r="T46" t="n">
-        <v>2.74</v>
+        <v>2.3</v>
       </c>
       <c r="U46" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="V46" t="n">
-        <v>6.55</v>
+        <v>5.25</v>
       </c>
       <c r="W46" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X46" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.81</v>
+        <v>2.23</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.14</v>
+        <v>2.48</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.12</v>
+        <v>1.49</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.61</v>
+        <v>2.42</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.64</v>
+        <v>1.58</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46052.64583333334</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,77 +6010,77 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46052.64583333334</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.24</v>
+        <v>2.55</v>
       </c>
       <c r="M48" t="n">
-        <v>3.37</v>
+        <v>2.95</v>
       </c>
       <c r="N48" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="O48" t="n">
-        <v>2.45</v>
+        <v>3.49</v>
       </c>
       <c r="P48" t="n">
-        <v>2.42</v>
+        <v>1.86</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.12</v>
+        <v>3.46</v>
       </c>
       <c r="R48" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="S48" t="n">
-        <v>3.18</v>
+        <v>2.29</v>
       </c>
       <c r="T48" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="U48" t="n">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="V48" t="n">
-        <v>5.25</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W48" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="X48" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="Z48" t="n">
-        <v>4.4</v>
+        <v>2.52</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.58</v>
+        <v>2.33</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.23</v>
+        <v>1.53</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.48</v>
+        <v>4.2</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.49</v>
+        <v>1.94</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.42</v>
+        <v>1.75</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.58</v>
+        <v>1.37</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46052.64583333334</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.34</v>
+        <v>3.35</v>
       </c>
       <c r="M49" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N49" t="n">
-        <v>3.05</v>
+        <v>2.08</v>
       </c>
       <c r="O49" t="n">
-        <v>3.17</v>
+        <v>4.27</v>
       </c>
       <c r="P49" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.72</v>
+        <v>2.9</v>
       </c>
       <c r="R49" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S49" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="T49" t="n">
-        <v>3.31</v>
+        <v>3.18</v>
       </c>
       <c r="U49" t="n">
         <v>1.28</v>
       </c>
       <c r="V49" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="W49" t="n">
         <v>1.06</v>
       </c>
       <c r="X49" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AC49" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46052.64583333334</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="M50" t="n">
         <v>2.95</v>
       </c>
       <c r="N50" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="O50" t="n">
-        <v>3.49</v>
+        <v>3.17</v>
       </c>
       <c r="P50" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.46</v>
+        <v>3.72</v>
       </c>
       <c r="R50" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S50" t="n">
-        <v>2.29</v>
+        <v>2.64</v>
       </c>
       <c r="T50" t="n">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="U50" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V50" t="n">
-        <v>8.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W50" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X50" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC50" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46052.64583333334</v>
@@ -6490,22 +6490,22 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="M51" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="N51" t="n">
         <v>2.75</v>
       </c>
       <c r="O51" t="n">
-        <v>3.09</v>
+        <v>2.85</v>
       </c>
       <c r="P51" t="n">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.4</v>
+        <v>3.61</v>
       </c>
       <c r="R51" t="n">
         <v>1.44</v>
@@ -6535,16 +6535,16 @@
         <v>2.92</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE51" t="n">
         <v>1.79</v>
@@ -6553,7 +6553,7 @@
         <v>1.92</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AH51" t="n">
         <v>1.52</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,73 +6609,73 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="M52" t="n">
-        <v>3.5</v>
+        <v>5.95</v>
       </c>
       <c r="N52" t="n">
-        <v>3.5</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O52" t="n">
-        <v>2.45</v>
+        <v>1.62</v>
       </c>
       <c r="P52" t="n">
-        <v>2.32</v>
+        <v>2.91</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.72</v>
+        <v>6.7</v>
       </c>
       <c r="R52" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="S52" t="n">
-        <v>3.44</v>
+        <v>4.45</v>
       </c>
       <c r="T52" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="U52" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="V52" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="W52" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="X52" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z52" t="n">
-        <v>4.75</v>
+        <v>6.95</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AB52" t="n">
-        <v>2.43</v>
+        <v>3.14</v>
       </c>
       <c r="AC52" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.59</v>
+        <v>1.98</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.75</v>
+        <v>3.95</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46052.66666666666</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,73 +6728,73 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="M53" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N53" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="O53" t="n">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="P53" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="R53" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S53" t="n">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
       <c r="T53" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="U53" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V53" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X53" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD53" t="n">
         <v>1.59</v>
       </c>
-      <c r="V53" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X53" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AE53" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46052.66666666666</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="M54" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="O54" t="n">
-        <v>2.53</v>
+        <v>2.02</v>
       </c>
       <c r="P54" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.62</v>
+        <v>5</v>
       </c>
       <c r="R54" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S54" t="n">
-        <v>3.44</v>
+        <v>3.52</v>
       </c>
       <c r="T54" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="U54" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="V54" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="W54" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X54" t="n">
         <v>1.01</v>
       </c>
       <c r="Y54" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG54" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z54" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH54" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46052.66666666666</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="M55" t="n">
-        <v>3.01</v>
+        <v>3.4</v>
       </c>
       <c r="N55" t="n">
-        <v>3.57</v>
+        <v>2.8</v>
       </c>
       <c r="O55" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="P55" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="Q55" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="R55" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="S55" t="n">
-        <v>2.65</v>
+        <v>3.52</v>
       </c>
       <c r="T55" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="U55" t="n">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="V55" t="n">
-        <v>8.4</v>
+        <v>5.1</v>
       </c>
       <c r="W55" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X55" t="n">
         <v>1.02</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.89</v>
+        <v>4.95</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.65</v>
+        <v>2.33</v>
       </c>
       <c r="AC55" t="n">
-        <v>3.78</v>
+        <v>2.33</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.19</v>
+        <v>1.57</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.87</v>
+        <v>1.46</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,34 +7085,34 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.13</v>
+        <v>2.95</v>
       </c>
       <c r="M56" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="N56" t="n">
-        <v>3.08</v>
+        <v>2.25</v>
       </c>
       <c r="O56" t="n">
-        <v>2.54</v>
+        <v>3.5</v>
       </c>
       <c r="P56" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.83</v>
+        <v>2.8</v>
       </c>
       <c r="R56" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S56" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="T56" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="U56" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="V56" t="n">
         <v>7.5</v>
@@ -7121,37 +7121,37 @@
         <v>1.03</v>
       </c>
       <c r="X56" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y56" t="n">
         <v>1.3</v>
       </c>
       <c r="Z56" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AC56" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AF56" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,73 +7204,73 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.31</v>
+        <v>1.72</v>
       </c>
       <c r="M57" t="n">
-        <v>3.3</v>
+        <v>3.88</v>
       </c>
       <c r="N57" t="n">
-        <v>2.9</v>
+        <v>4.33</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,73 +7323,73 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3.39</v>
+        <v>2.2</v>
       </c>
       <c r="M58" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="N58" t="n">
-        <v>1.94</v>
+        <v>3.3</v>
       </c>
       <c r="O58" t="n">
-        <v>4.3</v>
+        <v>2.54</v>
       </c>
       <c r="P58" t="n">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.63</v>
+        <v>3.83</v>
       </c>
       <c r="R58" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S58" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="T58" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="U58" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V58" t="n">
         <v>7.5</v>
       </c>
       <c r="W58" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X58" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z58" t="n">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AC58" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="AD58" t="n">
         <v>1.25</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.26</v>
+        <v>1.61</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,73 +7561,73 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="M60" t="n">
-        <v>2.84</v>
+        <v>3.4</v>
       </c>
       <c r="N60" t="n">
-        <v>3.16</v>
+        <v>2.8</v>
       </c>
       <c r="O60" t="n">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="P60" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.18</v>
+        <v>3.62</v>
       </c>
       <c r="R60" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="S60" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V60" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X60" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF60" t="n">
         <v>2.53</v>
       </c>
-      <c r="T60" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U60" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V60" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W60" t="n">
-        <v>1</v>
-      </c>
-      <c r="X60" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE60" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AG60" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AI60" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,73 +7680,73 @@
         </is>
       </c>
       <c r="L61" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M61" t="n">
+        <v>3</v>
+      </c>
+      <c r="N61" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O61" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P61" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S61" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V61" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W61" t="n">
+        <v>1</v>
+      </c>
+      <c r="X61" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF61" t="n">
         <v>1.72</v>
       </c>
-      <c r="M61" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="N61" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="O61" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P61" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R61" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S61" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T61" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U61" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V61" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="W61" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X61" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA61" t="n">
+      <c r="AG61" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH61" t="n">
         <v>1.58</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH61" t="n">
-        <v>2.01</v>
       </c>
       <c r="AI61" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,73 +7799,73 @@
         </is>
       </c>
       <c r="L62" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M62" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N62" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="O62" t="n">
+        <v>4</v>
+      </c>
+      <c r="P62" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S62" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V62" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W62" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X62" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG62" t="n">
         <v>1.25</v>
       </c>
-      <c r="M62" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="N62" t="n">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="O62" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="P62" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="R62" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S62" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="T62" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U62" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V62" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="W62" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AH62" t="n">
-        <v>3.95</v>
+        <v>1.29</v>
       </c>
       <c r="AI62" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,73 +7918,73 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>4.1</v>
+        <v>3.64</v>
       </c>
       <c r="M63" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N63" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="O63" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="P63" t="n">
-        <v>2.27</v>
+        <v>2.03</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.42</v>
+        <v>2.63</v>
       </c>
       <c r="R63" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S63" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V63" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG63" t="n">
         <v>1.3</v>
       </c>
-      <c r="S63" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T63" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U63" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V63" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W63" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X63" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG63" t="n">
+      <c r="AH63" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AH63" t="n">
-        <v>1.29</v>
       </c>
       <c r="AI63" s="3" t="n">
         <v>46052.66666666666</v>
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.3</v>
+        <v>2.68</v>
       </c>
       <c r="M64" t="n">
         <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="O64" t="n">
         <v>3.2</v>
@@ -8058,7 +8058,7 @@
         <v>1.4</v>
       </c>
       <c r="S64" t="n">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="T64" t="n">
         <v>2.82</v>
@@ -8082,16 +8082,16 @@
         <v>3.24</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AC64" t="n">
         <v>3.25</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE64" t="n">
         <v>1.68</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,73 +8156,73 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.56</v>
+        <v>2.02</v>
       </c>
       <c r="M65" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N65" t="n">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="O65" t="n">
-        <v>3.5</v>
+        <v>2.74</v>
       </c>
       <c r="P65" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="R65" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S65" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="T65" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U65" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V65" t="n">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="W65" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X65" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z65" t="n">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AC65" t="n">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.38</v>
+        <v>1.72</v>
       </c>
       <c r="AI65" s="3" t="n">
         <v>46052.66666666666</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,73 +8275,73 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.53</v>
+        <v>2.31</v>
       </c>
       <c r="M66" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N66" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="O66" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AI66" s="3" t="n">
         <v>46052.66666666666</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,73 +8394,73 @@
         </is>
       </c>
       <c r="L67" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M67" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N67" t="n">
         <v>2.59</v>
       </c>
-      <c r="M67" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="N67" t="n">
-        <v>2.53</v>
-      </c>
       <c r="O67" t="n">
-        <v>3.06</v>
+        <v>2.84</v>
       </c>
       <c r="P67" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="Q67" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="R67" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="S67" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="T67" t="n">
-        <v>2.27</v>
+        <v>2.66</v>
       </c>
       <c r="U67" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V67" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="W67" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH67" t="n">
         <v>1.53</v>
-      </c>
-      <c r="V67" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W67" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X67" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AE67" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AF67" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG67" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AH67" t="n">
-        <v>1.42</v>
       </c>
       <c r="AI67" s="3" t="n">
         <v>46052.67708333334</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,73 +8513,73 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="M68" t="n">
-        <v>3.12</v>
+        <v>3.38</v>
       </c>
       <c r="N68" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O68" t="n">
-        <v>2.84</v>
+        <v>3.06</v>
       </c>
       <c r="P68" t="n">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R68" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="S68" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="T68" t="n">
-        <v>2.66</v>
+        <v>2.27</v>
       </c>
       <c r="U68" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="V68" t="n">
-        <v>6.55</v>
+        <v>5.1</v>
       </c>
       <c r="W68" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X68" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z68" t="n">
-        <v>3.42</v>
+        <v>4.55</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.87</v>
+        <v>2.29</v>
       </c>
       <c r="AC68" t="n">
-        <v>2.97</v>
+        <v>2.3</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="AF68" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="AG68" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AI68" s="3" t="n">
         <v>46052.67708333334</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,73 +8751,73 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD70" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI70" s="3" t="n">
         <v>46052.6875</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,73 +8989,73 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI72" s="3" t="n">
         <v>46052.6875</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,73 +9108,73 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U73" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD73" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH73" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AI73" s="3" t="n">
         <v>46052.6875</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,73 +9227,73 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U74" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V74" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH74" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI74" s="3" t="n">
         <v>46052.6875</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,73 +9465,73 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.68</v>
+        <v>1.42</v>
       </c>
       <c r="M76" t="n">
-        <v>3.5</v>
+        <v>4.84</v>
       </c>
       <c r="N76" t="n">
-        <v>4.7</v>
+        <v>8.5</v>
       </c>
       <c r="O76" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="P76" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.04</v>
+        <v>6.7</v>
       </c>
       <c r="R76" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="S76" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V76" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W76" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X76" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC76" t="n">
         <v>2.7</v>
       </c>
-      <c r="T76" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U76" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V76" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W76" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X76" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA76" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB76" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC76" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AD76" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG76" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.91</v>
+        <v>2.8</v>
       </c>
       <c r="AI76" s="3" t="n">
         <v>46052.69791666666</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,73 +9584,73 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.85</v>
+        <v>2.77</v>
       </c>
       <c r="M77" t="n">
-        <v>3.29</v>
+        <v>3.05</v>
       </c>
       <c r="N77" t="n">
-        <v>4.4</v>
+        <v>2.32</v>
       </c>
       <c r="O77" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="P77" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.8</v>
+        <v>3.26</v>
       </c>
       <c r="R77" t="n">
-        <v>1.64</v>
+        <v>1.37</v>
       </c>
       <c r="S77" t="n">
-        <v>2.4</v>
+        <v>2.77</v>
       </c>
       <c r="T77" t="n">
-        <v>3.82</v>
+        <v>2.77</v>
       </c>
       <c r="U77" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="V77" t="n">
-        <v>10.5</v>
+        <v>6.7</v>
       </c>
       <c r="W77" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X77" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.53</v>
+        <v>3.55</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AC77" t="n">
-        <v>5.25</v>
+        <v>3.4</v>
       </c>
       <c r="AD77" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AE77" t="n">
-        <v>2.15</v>
+        <v>1.69</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AG77" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.81</v>
+        <v>1.45</v>
       </c>
       <c r="AI77" s="3" t="n">
         <v>46052.69791666666</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,73 +9703,73 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.42</v>
+        <v>2.05</v>
       </c>
       <c r="M78" t="n">
-        <v>4.84</v>
+        <v>3.15</v>
       </c>
       <c r="N78" t="n">
-        <v>8.5</v>
+        <v>4.2</v>
       </c>
       <c r="O78" t="n">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="P78" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R78" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S78" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T78" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V78" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="W78" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X78" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AA78" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q78" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="R78" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S78" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T78" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U78" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V78" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W78" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X78" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y78" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z78" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA78" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AB78" t="n">
-        <v>2.2</v>
+        <v>1.49</v>
       </c>
       <c r="AC78" t="n">
-        <v>2.7</v>
+        <v>5.25</v>
       </c>
       <c r="AD78" t="n">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG78" t="n">
         <v>1.22</v>
       </c>
       <c r="AH78" t="n">
-        <v>2.8</v>
+        <v>1.81</v>
       </c>
       <c r="AI78" s="3" t="n">
         <v>46052.69791666666</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,73 +9822,73 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.77</v>
+        <v>1.68</v>
       </c>
       <c r="M79" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="N79" t="n">
-        <v>2.32</v>
+        <v>4.7</v>
       </c>
       <c r="O79" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P79" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S79" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V79" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W79" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X79" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z79" t="n">
         <v>3.2</v>
       </c>
-      <c r="P79" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="R79" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S79" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T79" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U79" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V79" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W79" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X79" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>3.55</v>
-      </c>
       <c r="AA79" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC79" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AD79" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="AF79" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AG79" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.45</v>
+        <v>1.91</v>
       </c>
       <c r="AI79" s="3" t="n">
         <v>46052.69791666666</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,73 +9941,73 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M80" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="N80" t="n">
         <v>3.7</v>
       </c>
       <c r="O80" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="P80" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q80" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="R80" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S80" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="T80" t="n">
-        <v>3.58</v>
+        <v>2.99</v>
       </c>
       <c r="U80" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="V80" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W80" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X80" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="Z80" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AC80" t="n">
-        <v>4.75</v>
+        <v>3.81</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AE80" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="AG80" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AI80" s="3" t="n">
         <v>46052.70833333334</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,73 +10060,73 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="M81" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="N81" t="n">
         <v>3.7</v>
       </c>
       <c r="O81" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="P81" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="R81" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S81" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="T81" t="n">
-        <v>2.99</v>
+        <v>3.58</v>
       </c>
       <c r="U81" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="V81" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W81" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X81" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="Z81" t="n">
-        <v>3.15</v>
+        <v>2.55</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AC81" t="n">
-        <v>3.81</v>
+        <v>4.75</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="AG81" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AI81" s="3" t="n">
         <v>46052.70833333334</v>
@@ -10179,73 +10179,73 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W82" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X82" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG82" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH82" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI82" s="3" t="n">
         <v>46052.73958333334</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O3" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.46</v>
+        <v>2.41</v>
       </c>
       <c r="R3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="T3" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>7</v>
+        <v>6.15</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.32</v>
+        <v>2.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE3" t="n">
         <v>1.69</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.2</v>
+        <v>1.79</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46052.22916666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V4" t="n">
+        <v>7</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1.82</v>
       </c>
-      <c r="O4" t="n">
-        <v>4</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V4" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AC4" t="n">
-        <v>2.88</v>
+        <v>3.32</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE4" t="n">
         <v>1.69</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.79</v>
+        <v>1.2</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46052.22916666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.33</v>
+        <v>1.83</v>
       </c>
       <c r="M18" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="O18" t="n">
-        <v>5.97</v>
+        <v>2.3</v>
       </c>
       <c r="P18" t="n">
-        <v>1.64</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.81</v>
+        <v>3.9</v>
       </c>
       <c r="R18" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>2.25</v>
+        <v>3.12</v>
       </c>
       <c r="T18" t="n">
-        <v>4.2</v>
+        <v>2.38</v>
       </c>
       <c r="U18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.16</v>
       </c>
-      <c r="V18" t="n">
-        <v>11</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.69</v>
-      </c>
       <c r="Z18" t="n">
-        <v>2.08</v>
+        <v>4.15</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.97</v>
+        <v>1.67</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.3</v>
+        <v>2.12</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.85</v>
+        <v>2.56</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.07</v>
+        <v>1.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.51</v>
+        <v>1.61</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.46</v>
+        <v>2.23</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.19</v>
+        <v>1.79</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46052.5</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46052.5</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46052.5</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.18</v>
+        <v>4.33</v>
       </c>
       <c r="M21" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="N21" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>1.57</v>
+        <v>4.75</v>
       </c>
       <c r="P21" t="n">
-        <v>2.7</v>
+        <v>1.92</v>
       </c>
       <c r="Q21" t="n">
-        <v>9.5</v>
+        <v>2.81</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="S21" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="T21" t="n">
-        <v>2.34</v>
+        <v>4.2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.52</v>
+        <v>1.23</v>
       </c>
       <c r="V21" t="n">
-        <v>5.05</v>
+        <v>11</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.16</v>
+        <v>1.7</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.35</v>
+        <v>2.08</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.55</v>
+        <v>3.04</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.28</v>
+        <v>1.29</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.45</v>
+        <v>5.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.52</v>
+        <v>1.07</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="AH21" t="n">
-        <v>4.33</v>
+        <v>1.12</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46052.5</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.6</v>
+        <v>1.07</v>
       </c>
       <c r="M26" t="n">
-        <v>3.34</v>
+        <v>10</v>
       </c>
       <c r="N26" t="n">
-        <v>1.7</v>
+        <v>16.53</v>
       </c>
       <c r="O26" t="n">
-        <v>4.75</v>
+        <v>1.32</v>
       </c>
       <c r="P26" t="n">
-        <v>2.02</v>
+        <v>3.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.34</v>
+        <v>13</v>
       </c>
       <c r="R26" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="S26" t="n">
-        <v>2.64</v>
+        <v>5.3</v>
       </c>
       <c r="T26" t="n">
-        <v>2.99</v>
+        <v>1.69</v>
       </c>
       <c r="U26" t="n">
-        <v>1.33</v>
+        <v>2.01</v>
       </c>
       <c r="V26" t="n">
-        <v>7.6</v>
+        <v>3.14</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="X26" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.05</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.12</v>
+        <v>1.18</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.66</v>
+        <v>4.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.58</v>
+        <v>1.49</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.26</v>
+        <v>2.27</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.28</v>
+        <v>1.02</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.15</v>
+        <v>6.8</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46052.58333333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="M27" t="n">
-        <v>3.24</v>
+        <v>3.34</v>
       </c>
       <c r="N27" t="n">
-        <v>2.49</v>
+        <v>1.7</v>
       </c>
       <c r="O27" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="P27" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.04</v>
+        <v>2.34</v>
       </c>
       <c r="R27" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S27" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T27" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
         <v>7.6</v>
       </c>
       <c r="W27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X27" t="n">
         <v>1.03</v>
       </c>
-      <c r="X27" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y27" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="AD27" t="n">
         <v>1.26</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.42</v>
+        <v>1.15</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46052.58333333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="N28" t="n">
-        <v>2.95</v>
+        <v>2.49</v>
       </c>
       <c r="O28" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="P28" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.65</v>
+        <v>3.04</v>
       </c>
       <c r="R28" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S28" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="T28" t="n">
-        <v>3.07</v>
+        <v>3.02</v>
       </c>
       <c r="U28" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="W28" t="n">
         <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AE28" t="n">
         <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46052.58333333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,70 +3872,70 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>3.07</v>
+        <v>2.95</v>
       </c>
       <c r="O29" t="n">
         <v>2.88</v>
       </c>
       <c r="P29" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.73</v>
+        <v>3.65</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S29" t="n">
         <v>2.77</v>
       </c>
       <c r="T29" t="n">
-        <v>2.69</v>
+        <v>3.07</v>
       </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="V29" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.28</v>
+        <v>2.97</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
         <v>1.56</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.07</v>
+        <v>2.23</v>
       </c>
       <c r="M31" t="n">
-        <v>10</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>16.53</v>
+        <v>3.07</v>
       </c>
       <c r="O31" t="n">
-        <v>1.32</v>
+        <v>2.88</v>
       </c>
       <c r="P31" t="n">
-        <v>3.95</v>
+        <v>2.07</v>
       </c>
       <c r="Q31" t="n">
-        <v>13</v>
+        <v>3.73</v>
       </c>
       <c r="R31" t="n">
-        <v>1.15</v>
+        <v>1.38</v>
       </c>
       <c r="S31" t="n">
-        <v>5.3</v>
+        <v>2.77</v>
       </c>
       <c r="T31" t="n">
-        <v>1.69</v>
+        <v>2.69</v>
       </c>
       <c r="U31" t="n">
-        <v>2.01</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>3.14</v>
+        <v>6.25</v>
       </c>
       <c r="W31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AG31" t="n">
         <v>1.3</v>
       </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AH31" t="n">
-        <v>6.8</v>
+        <v>1.56</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46052.58333333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.5</v>
+        <v>9.85</v>
       </c>
       <c r="M33" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="O33" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="P33" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V33" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB33" t="n">
         <v>3.5</v>
       </c>
-      <c r="N33" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O33" t="n">
-        <v>3</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V33" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X33" t="n">
+      <c r="AC33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AH33" t="n">
         <v>1.02</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.45</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46052.60416666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46052.60416666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>9.85</v>
+        <v>2.5</v>
       </c>
       <c r="M35" t="n">
-        <v>6.65</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V35" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y35" t="n">
         <v>1.17</v>
       </c>
-      <c r="O35" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="P35" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="S35" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V35" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Z35" t="n">
-        <v>7.7</v>
+        <v>5.47</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="AB35" t="n">
-        <v>3.5</v>
+        <v>2.53</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.7</v>
+        <v>2.27</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.06</v>
+        <v>1.63</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.21</v>
+        <v>2.63</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46052.60416666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46052.60416666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="N37" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P37" t="n">
         <v>2</v>
       </c>
-      <c r="M37" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N37" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O37" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1.77</v>
-      </c>
       <c r="Q37" t="n">
-        <v>6.26</v>
+        <v>7.5</v>
       </c>
       <c r="R37" t="n">
-        <v>1.74</v>
+        <v>1.47</v>
       </c>
       <c r="S37" t="n">
-        <v>2.04</v>
+        <v>2.44</v>
       </c>
       <c r="T37" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="U37" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="V37" t="n">
-        <v>15</v>
+        <v>7.9</v>
       </c>
       <c r="W37" t="n">
         <v>1.02</v>
       </c>
       <c r="X37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AD37" t="n">
         <v>1.17</v>
       </c>
-      <c r="Y37" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AE37" t="n">
-        <v>2.64</v>
+        <v>2.31</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.77</v>
+        <v>2.38</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46052.625</v>
@@ -4943,19 +4943,19 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="M38" t="n">
         <v>2.75</v>
       </c>
       <c r="N38" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="O38" t="n">
-        <v>3.8</v>
+        <v>4.39</v>
       </c>
       <c r="P38" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q38" t="n">
         <v>3</v>
@@ -4967,7 +4967,7 @@
         <v>2.15</v>
       </c>
       <c r="T38" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="U38" t="n">
         <v>1.22</v>
@@ -4985,7 +4985,7 @@
         <v>1.52</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="AA38" t="n">
         <v>2.49</v>
@@ -5003,7 +5003,7 @@
         <v>2.09</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG38" t="n">
         <v>1.36</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.47</v>
+        <v>2.6</v>
       </c>
       <c r="M39" t="n">
-        <v>3.76</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>6.84</v>
+        <v>2.25</v>
       </c>
       <c r="O39" t="n">
-        <v>2.11</v>
+        <v>3</v>
       </c>
       <c r="P39" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="Q39" t="n">
-        <v>7.5</v>
+        <v>2.88</v>
       </c>
       <c r="R39" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="S39" t="n">
-        <v>2.44</v>
+        <v>3.12</v>
       </c>
       <c r="T39" t="n">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="U39" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="V39" t="n">
-        <v>7.9</v>
+        <v>5.5</v>
       </c>
       <c r="W39" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X39" t="n">
         <v>1.04</v>
       </c>
       <c r="Y39" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AD39" t="n">
         <v>1.42</v>
       </c>
-      <c r="Z39" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AE39" t="n">
-        <v>2.31</v>
+        <v>1.55</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.38</v>
+        <v>1.39</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46052.625</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="N40" t="n">
-        <v>2.25</v>
+        <v>4.5</v>
       </c>
       <c r="O40" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="P40" t="n">
-        <v>2.38</v>
+        <v>1.77</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.88</v>
+        <v>6.21</v>
       </c>
       <c r="R40" t="n">
-        <v>1.29</v>
+        <v>1.74</v>
       </c>
       <c r="S40" t="n">
-        <v>3.12</v>
+        <v>1.93</v>
       </c>
       <c r="T40" t="n">
-        <v>2.36</v>
+        <v>4.33</v>
       </c>
       <c r="U40" t="n">
-        <v>1.49</v>
+        <v>1.13</v>
       </c>
       <c r="V40" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="W40" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X40" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.16</v>
+        <v>1.76</v>
       </c>
       <c r="Z40" t="n">
-        <v>4.05</v>
+        <v>2.04</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.66</v>
+        <v>3.39</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.15</v>
+        <v>1.26</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.61</v>
+        <v>7.5</v>
       </c>
       <c r="AD40" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AF40" t="n">
         <v>1.42</v>
       </c>
-      <c r="AE40" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AG40" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.39</v>
+        <v>1.77</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46052.625</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="M41" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N41" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="O41" t="n">
-        <v>2.62</v>
+        <v>3.17</v>
       </c>
       <c r="P41" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.2</v>
+        <v>3.72</v>
       </c>
       <c r="R41" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="S41" t="n">
-        <v>2.31</v>
+        <v>2.64</v>
       </c>
       <c r="T41" t="n">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="U41" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V41" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="W41" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X41" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC41" t="n">
-        <v>4.32</v>
+        <v>4</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46052.64583333334</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M43" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V43" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y43" t="n">
         <v>1.41</v>
       </c>
-      <c r="M43" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="N43" t="n">
-        <v>7</v>
-      </c>
-      <c r="O43" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>7</v>
-      </c>
-      <c r="R43" t="n">
+      <c r="Z43" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH43" t="n">
         <v>1.37</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V43" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>2.64</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46052.64583333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="M44" t="n">
-        <v>3.1</v>
+        <v>3.37</v>
       </c>
       <c r="N44" t="n">
-        <v>3.7</v>
+        <v>2.66</v>
       </c>
       <c r="O44" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="P44" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.85</v>
+        <v>3.12</v>
       </c>
       <c r="R44" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="S44" t="n">
-        <v>2.56</v>
+        <v>3.18</v>
       </c>
       <c r="T44" t="n">
-        <v>3.14</v>
+        <v>2.3</v>
       </c>
       <c r="U44" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="V44" t="n">
-        <v>8</v>
+        <v>5.25</v>
       </c>
       <c r="W44" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X44" t="n">
         <v>1.02</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.92</v>
+        <v>4.4</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.06</v>
+        <v>1.58</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.7</v>
+        <v>2.23</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.58</v>
+        <v>2.48</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.87</v>
+        <v>1.49</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.79</v>
+        <v>2.42</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46052.64583333334</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.24</v>
+        <v>3.35</v>
       </c>
       <c r="M46" t="n">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="N46" t="n">
-        <v>2.66</v>
+        <v>2.08</v>
       </c>
       <c r="O46" t="n">
-        <v>2.45</v>
+        <v>4.27</v>
       </c>
       <c r="P46" t="n">
-        <v>2.42</v>
+        <v>2.06</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="R46" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U46" t="n">
         <v>1.28</v>
       </c>
-      <c r="S46" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.55</v>
-      </c>
       <c r="V46" t="n">
-        <v>5.25</v>
+        <v>8.5</v>
       </c>
       <c r="W46" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X46" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="Z46" t="n">
-        <v>4.4</v>
+        <v>2.69</v>
       </c>
       <c r="AA46" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB46" t="n">
         <v>1.58</v>
       </c>
-      <c r="AB46" t="n">
-        <v>2.23</v>
-      </c>
       <c r="AC46" t="n">
-        <v>2.48</v>
+        <v>4.05</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.46</v>
+        <v>1.16</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.49</v>
+        <v>1.92</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.42</v>
+        <v>1.77</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46052.64583333334</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,77 +6010,77 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46052.64583333334</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,77 +6129,77 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46052.64583333334</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.35</v>
+        <v>1.41</v>
       </c>
       <c r="M49" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="N49" t="n">
-        <v>2.08</v>
+        <v>7</v>
       </c>
       <c r="O49" t="n">
-        <v>4.27</v>
+        <v>1.91</v>
       </c>
       <c r="P49" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.9</v>
+        <v>7</v>
       </c>
       <c r="R49" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="S49" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="T49" t="n">
-        <v>3.18</v>
+        <v>2.74</v>
       </c>
       <c r="U49" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="V49" t="n">
-        <v>8.5</v>
+        <v>6.55</v>
       </c>
       <c r="W49" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.23</v>
+        <v>1.9</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="AC49" t="n">
-        <v>4.05</v>
+        <v>3.14</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.3</v>
+        <v>2.64</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46052.64583333334</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="M50" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="N50" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O50" t="n">
-        <v>3.17</v>
+        <v>2.62</v>
       </c>
       <c r="P50" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.72</v>
+        <v>4.2</v>
       </c>
       <c r="R50" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="S50" t="n">
-        <v>2.64</v>
+        <v>2.31</v>
       </c>
       <c r="T50" t="n">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="U50" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V50" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W50" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X50" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC50" t="n">
-        <v>4</v>
+        <v>4.32</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46052.64583333334</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,73 +6609,73 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="M52" t="n">
-        <v>5.95</v>
+        <v>3.4</v>
       </c>
       <c r="N52" t="n">
-        <v>8.449999999999999</v>
+        <v>2.8</v>
       </c>
       <c r="O52" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P52" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S52" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V52" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X52" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH52" t="n">
         <v>1.62</v>
-      </c>
-      <c r="P52" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S52" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="T52" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V52" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>3.95</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46052.66666666666</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,73 +6728,73 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="M53" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N53" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="O53" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="P53" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.72</v>
+        <v>3.62</v>
       </c>
       <c r="R53" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S53" t="n">
         <v>3.44</v>
       </c>
       <c r="T53" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="U53" t="n">
         <v>1.6</v>
       </c>
       <c r="V53" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="W53" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X53" t="n">
         <v>1.01</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="Z53" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="AC53" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46052.66666666666</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.53</v>
+        <v>3.15</v>
       </c>
       <c r="M54" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N54" t="n">
-        <v>5</v>
+        <v>2.12</v>
       </c>
       <c r="O54" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46052.66666666666</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="M55" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N55" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="O55" t="n">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="P55" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="R55" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S55" t="n">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
       <c r="T55" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="U55" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V55" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD55" t="n">
         <v>1.59</v>
       </c>
-      <c r="V55" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X55" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AE55" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,73 +7085,73 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.95</v>
+        <v>2.31</v>
       </c>
       <c r="M56" t="n">
         <v>3.3</v>
       </c>
       <c r="N56" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="O56" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,73 +7204,73 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.72</v>
+        <v>2.95</v>
       </c>
       <c r="M57" t="n">
-        <v>3.88</v>
+        <v>3.3</v>
       </c>
       <c r="N57" t="n">
-        <v>4.33</v>
+        <v>2.25</v>
       </c>
       <c r="O57" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P57" t="n">
         <v>2.1</v>
       </c>
-      <c r="P57" t="n">
-        <v>2.29</v>
-      </c>
       <c r="Q57" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="R57" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S57" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V57" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X57" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG57" t="n">
         <v>1.28</v>
       </c>
-      <c r="S57" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T57" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V57" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X57" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH57" t="n">
-        <v>2.01</v>
+        <v>1.38</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,73 +7323,73 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="M58" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N58" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="O58" t="n">
-        <v>2.54</v>
+        <v>2.02</v>
       </c>
       <c r="P58" t="n">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.83</v>
+        <v>5</v>
       </c>
       <c r="R58" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="S58" t="n">
-        <v>2.73</v>
+        <v>3.52</v>
       </c>
       <c r="T58" t="n">
-        <v>2.89</v>
+        <v>2.17</v>
       </c>
       <c r="U58" t="n">
-        <v>1.42</v>
+        <v>1.63</v>
       </c>
       <c r="V58" t="n">
-        <v>7.5</v>
+        <v>4.8</v>
       </c>
       <c r="W58" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X58" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="Z58" t="n">
-        <v>3.24</v>
+        <v>4.9</v>
       </c>
       <c r="AA58" t="n">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.84</v>
+        <v>2.43</v>
       </c>
       <c r="AC58" t="n">
-        <v>3.4</v>
+        <v>2.28</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AF58" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.61</v>
+        <v>2.35</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,73 +7442,73 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="M59" t="n">
         <v>3.45</v>
       </c>
       <c r="N59" t="n">
-        <v>2.12</v>
+        <v>1.86</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI59" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,73 +7561,73 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="M60" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N60" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O60" t="n">
         <v>2.8</v>
       </c>
-      <c r="O60" t="n">
-        <v>2.53</v>
-      </c>
       <c r="P60" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.62</v>
+        <v>4.18</v>
       </c>
       <c r="R60" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="S60" t="n">
-        <v>3.44</v>
+        <v>2.34</v>
       </c>
       <c r="T60" t="n">
-        <v>2.23</v>
+        <v>3.25</v>
       </c>
       <c r="U60" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="V60" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1</v>
+      </c>
+      <c r="X60" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC60" t="n">
         <v>4.75</v>
       </c>
-      <c r="W60" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X60" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y60" t="n">
+      <c r="AD60" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z60" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD60" t="n">
+      <c r="AE60" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH60" t="n">
         <v>1.58</v>
-      </c>
-      <c r="AE60" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH60" t="n">
-        <v>1.7</v>
       </c>
       <c r="AI60" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,73 +7680,73 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="M61" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N61" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O61" t="n">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="P61" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S61" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V61" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W61" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA61" t="n">
         <v>2</v>
       </c>
-      <c r="Q61" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="R61" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S61" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T61" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U61" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V61" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W61" t="n">
-        <v>1</v>
-      </c>
-      <c r="X61" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>2.51</v>
-      </c>
       <c r="AB61" t="n">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="AC61" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE61" t="n">
-        <v>2.01</v>
+        <v>1.73</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AG61" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AI61" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,73 +7799,73 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>4.1</v>
+        <v>1.72</v>
       </c>
       <c r="M62" t="n">
-        <v>3.45</v>
+        <v>3.88</v>
       </c>
       <c r="N62" t="n">
-        <v>1.86</v>
+        <v>4.33</v>
       </c>
       <c r="O62" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="P62" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.42</v>
+        <v>4.4</v>
       </c>
       <c r="R62" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S62" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="T62" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="U62" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="V62" t="n">
-        <v>5.5</v>
+        <v>5.15</v>
       </c>
       <c r="W62" t="n">
         <v>1.1</v>
       </c>
       <c r="X62" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z62" t="n">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="AC62" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AF62" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AG62" t="n">
         <v>1.25</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.29</v>
+        <v>2.01</v>
       </c>
       <c r="AI62" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,73 +7918,73 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.64</v>
+        <v>1.25</v>
       </c>
       <c r="M63" t="n">
-        <v>3.35</v>
+        <v>5.95</v>
       </c>
       <c r="N63" t="n">
-        <v>1.95</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O63" t="n">
-        <v>4.3</v>
+        <v>1.62</v>
       </c>
       <c r="P63" t="n">
-        <v>2.03</v>
+        <v>2.91</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.63</v>
+        <v>6.7</v>
       </c>
       <c r="R63" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="S63" t="n">
-        <v>2.69</v>
+        <v>4.45</v>
       </c>
       <c r="T63" t="n">
-        <v>2.99</v>
+        <v>1.88</v>
       </c>
       <c r="U63" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="V63" t="n">
-        <v>7.5</v>
+        <v>3.7</v>
       </c>
       <c r="W63" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="X63" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="Z63" t="n">
-        <v>3.12</v>
+        <v>6.95</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.1</v>
+        <v>1.27</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.7</v>
+        <v>3.14</v>
       </c>
       <c r="AC63" t="n">
-        <v>3.44</v>
+        <v>1.79</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.25</v>
+        <v>1.98</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="AG63" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.25</v>
+        <v>3.95</v>
       </c>
       <c r="AI63" s="3" t="n">
         <v>46052.66666666666</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,73 +8037,73 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.68</v>
+        <v>2.02</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N64" t="n">
-        <v>2.63</v>
+        <v>3.75</v>
       </c>
       <c r="O64" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="P64" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.93</v>
+        <v>4</v>
       </c>
       <c r="R64" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S64" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="T64" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="U64" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V64" t="n">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="W64" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X64" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z64" t="n">
-        <v>3.24</v>
+        <v>2.89</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB64" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF64" t="n">
         <v>1.83</v>
       </c>
-      <c r="AC64" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE64" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF64" t="n">
-        <v>2</v>
-      </c>
       <c r="AG64" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="AI64" s="3" t="n">
         <v>46052.66666666666</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,73 +8156,73 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.02</v>
+        <v>2.68</v>
       </c>
       <c r="M65" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N65" t="n">
-        <v>3.75</v>
+        <v>2.63</v>
       </c>
       <c r="O65" t="n">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="P65" t="n">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="Q65" t="n">
-        <v>4</v>
+        <v>2.93</v>
       </c>
       <c r="R65" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S65" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="T65" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="U65" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V65" t="n">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="W65" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X65" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.89</v>
+        <v>3.24</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AC65" t="n">
-        <v>3.78</v>
+        <v>3.25</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="AI65" s="3" t="n">
         <v>46052.66666666666</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,73 +8275,73 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.31</v>
+        <v>3.64</v>
       </c>
       <c r="M66" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N66" t="n">
-        <v>2.9</v>
+        <v>1.95</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI66" s="3" t="n">
         <v>46052.66666666666</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,73 +8751,73 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U70" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V70" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI70" s="3" t="n">
         <v>46052.6875</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,73 +8989,73 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U72" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V72" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W72" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X72" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH72" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AI72" s="3" t="n">
         <v>46052.6875</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,73 +9227,73 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V74" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W74" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG74" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH74" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI74" s="3" t="n">
         <v>46052.6875</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,73 +9346,73 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T75" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V75" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W75" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD75" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG75" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH75" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI75" s="3" t="n">
         <v>46052.6875</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,73 +9584,73 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.77</v>
+        <v>1.73</v>
       </c>
       <c r="M77" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="N77" t="n">
-        <v>2.32</v>
+        <v>4.5</v>
       </c>
       <c r="O77" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P77" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="R77" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S77" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V77" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W77" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X77" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z77" t="n">
         <v>3.2</v>
       </c>
-      <c r="P77" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="R77" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S77" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T77" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U77" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V77" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W77" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X77" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y77" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z77" t="n">
-        <v>3.55</v>
-      </c>
       <c r="AA77" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AC77" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AD77" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AF77" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AG77" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.45</v>
+        <v>1.91</v>
       </c>
       <c r="AI77" s="3" t="n">
         <v>46052.69791666666</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,73 +9822,73 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.68</v>
+        <v>2.77</v>
       </c>
       <c r="M79" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="N79" t="n">
-        <v>4.7</v>
+        <v>2.32</v>
       </c>
       <c r="O79" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="P79" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.04</v>
+        <v>3.26</v>
       </c>
       <c r="R79" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S79" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="T79" t="n">
-        <v>2.63</v>
+        <v>2.77</v>
       </c>
       <c r="U79" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V79" t="n">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="W79" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X79" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z79" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC79" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AD79" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AG79" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.91</v>
+        <v>1.45</v>
       </c>
       <c r="AI79" s="3" t="n">
         <v>46052.69791666666</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,73 +9941,73 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="M80" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="N80" t="n">
         <v>3.7</v>
       </c>
       <c r="O80" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="P80" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="R80" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S80" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="T80" t="n">
-        <v>2.99</v>
+        <v>3.58</v>
       </c>
       <c r="U80" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="V80" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W80" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X80" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="Z80" t="n">
-        <v>3.15</v>
+        <v>2.55</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AC80" t="n">
-        <v>3.81</v>
+        <v>4.75</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="AG80" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AI80" s="3" t="n">
         <v>46052.70833333334</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,73 +10060,73 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M81" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="N81" t="n">
         <v>3.7</v>
       </c>
       <c r="O81" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="P81" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q81" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="R81" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S81" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="T81" t="n">
-        <v>3.58</v>
+        <v>2.99</v>
       </c>
       <c r="U81" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="V81" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W81" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X81" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="Z81" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AC81" t="n">
-        <v>4.75</v>
+        <v>3.81</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AE81" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="AG81" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AI81" s="3" t="n">
         <v>46052.70833333334</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -659,19 +659,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="N2" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="P2" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
         <v>2.5</v>
@@ -689,37 +689,37 @@
         <v>1.4</v>
       </c>
       <c r="V2" t="n">
-        <v>6.25</v>
+        <v>6.9</v>
       </c>
       <c r="W2" t="n">
         <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
         <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC2" t="n">
         <v>3.18</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE2" t="n">
         <v>1.7</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG2" t="n">
         <v>1.26</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V3" t="n">
+        <v>7</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB3" t="n">
         <v>1.82</v>
       </c>
-      <c r="O3" t="n">
-        <v>4</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V3" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AC3" t="n">
-        <v>2.88</v>
+        <v>3.32</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
         <v>1.69</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.79</v>
+        <v>1.2</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46052.22916666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O4" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.46</v>
+        <v>2.41</v>
       </c>
       <c r="R4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="T4" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>7</v>
+        <v>6.15</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.32</v>
+        <v>2.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE4" t="n">
         <v>1.69</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.2</v>
+        <v>1.79</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46052.22916666666</v>
@@ -1022,34 +1022,34 @@
         <v>3.8</v>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="O5" t="n">
         <v>2.62</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S5" t="n">
         <v>3.66</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="U5" t="n">
         <v>1.63</v>
       </c>
       <c r="V5" t="n">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
         <v>1.03</v>
@@ -1064,7 +1064,7 @@
         <v>1.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AC5" t="n">
         <v>2.25</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46052.5</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.83</v>
+        <v>4.33</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="N18" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>2.3</v>
+        <v>4.75</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.9</v>
+        <v>2.81</v>
       </c>
       <c r="R18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V18" t="n">
+        <v>11</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1.29</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V18" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W18" t="n">
+      <c r="AC18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.12</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.79</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46052.5</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46052.5</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,61 +2920,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.33</v>
+        <v>1.14</v>
       </c>
       <c r="M21" t="n">
-        <v>2.6</v>
+        <v>6.59</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>8.1</v>
       </c>
       <c r="O21" t="n">
-        <v>4.75</v>
+        <v>1.57</v>
       </c>
       <c r="P21" t="n">
-        <v>1.92</v>
+        <v>2.65</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.81</v>
+        <v>9.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>1.9</v>
+        <v>3.16</v>
       </c>
       <c r="T21" t="n">
-        <v>4.2</v>
+        <v>2.36</v>
       </c>
       <c r="U21" t="n">
-        <v>1.23</v>
+        <v>1.51</v>
       </c>
       <c r="V21" t="n">
-        <v>11</v>
+        <v>5.1</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.7</v>
+        <v>1.16</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.08</v>
+        <v>4.15</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.04</v>
+        <v>1.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.29</v>
+        <v>2.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.9</v>
+        <v>2.43</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.07</v>
+        <v>1.52</v>
       </c>
       <c r="AE21" t="n">
         <v>2.51</v>
@@ -2983,10 +2983,10 @@
         <v>1.46</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.41</v>
+        <v>1.08</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.12</v>
+        <v>4.3</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46052.5</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.07</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>10</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>16.53</v>
+        <v>2.95</v>
       </c>
       <c r="O26" t="n">
-        <v>1.32</v>
+        <v>2.88</v>
       </c>
       <c r="P26" t="n">
-        <v>3.95</v>
+        <v>2.09</v>
       </c>
       <c r="Q26" t="n">
-        <v>13</v>
+        <v>3.65</v>
       </c>
       <c r="R26" t="n">
-        <v>1.15</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>5.3</v>
+        <v>2.77</v>
       </c>
       <c r="T26" t="n">
-        <v>1.69</v>
+        <v>3.07</v>
       </c>
       <c r="U26" t="n">
-        <v>2.01</v>
+        <v>1.35</v>
       </c>
       <c r="V26" t="n">
-        <v>3.14</v>
+        <v>7.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="Z26" t="n">
-        <v>9.300000000000001</v>
+        <v>2.97</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.18</v>
+        <v>2.05</v>
       </c>
       <c r="AB26" t="n">
-        <v>4.2</v>
+        <v>1.73</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.49</v>
+        <v>3.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.27</v>
+        <v>1.21</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="AH26" t="n">
-        <v>6.8</v>
+        <v>1.56</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46052.58333333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="M27" t="n">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
       <c r="N27" t="n">
-        <v>1.7</v>
+        <v>2.49</v>
       </c>
       <c r="O27" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="P27" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.34</v>
+        <v>3.04</v>
       </c>
       <c r="R27" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S27" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T27" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="U27" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
         <v>7.6</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="AD27" t="n">
         <v>1.26</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.15</v>
+        <v>1.42</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46052.58333333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.9</v>
+        <v>1.07</v>
       </c>
       <c r="M28" t="n">
-        <v>3.24</v>
+        <v>10</v>
       </c>
       <c r="N28" t="n">
-        <v>2.49</v>
+        <v>16.53</v>
       </c>
       <c r="O28" t="n">
-        <v>3.25</v>
+        <v>1.32</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>3.95</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.04</v>
+        <v>13</v>
       </c>
       <c r="R28" t="n">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
       <c r="S28" t="n">
-        <v>2.62</v>
+        <v>5.3</v>
       </c>
       <c r="T28" t="n">
-        <v>3.02</v>
+        <v>1.69</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>2.01</v>
       </c>
       <c r="V28" t="n">
-        <v>7.6</v>
+        <v>3.14</v>
       </c>
       <c r="W28" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.42</v>
+        <v>6.8</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46052.58333333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.3</v>
+        <v>4.6</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.95</v>
+        <v>1.75</v>
       </c>
       <c r="O29" t="n">
-        <v>2.88</v>
+        <v>4.45</v>
       </c>
       <c r="P29" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.65</v>
+        <v>2.34</v>
       </c>
       <c r="R29" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S29" t="n">
-        <v>2.77</v>
+        <v>2.54</v>
       </c>
       <c r="T29" t="n">
-        <v>3.07</v>
+        <v>2.99</v>
       </c>
       <c r="U29" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V29" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="W29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X29" t="n">
         <v>1.03</v>
       </c>
-      <c r="X29" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y29" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD29" t="n">
         <v>1.21</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AG29" t="n">
         <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.56</v>
+        <v>1.15</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46052.58333333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>9.85</v>
+        <v>1.95</v>
       </c>
       <c r="M33" t="n">
-        <v>6.65</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>1.17</v>
+        <v>3.4</v>
       </c>
       <c r="O33" t="n">
-        <v>7.39</v>
+        <v>2.48</v>
       </c>
       <c r="P33" t="n">
-        <v>3.12</v>
+        <v>2.19</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.52</v>
+        <v>4.21</v>
       </c>
       <c r="R33" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>4.85</v>
+        <v>3.25</v>
       </c>
       <c r="T33" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.9</v>
+        <v>1.47</v>
       </c>
       <c r="V33" t="n">
-        <v>3.45</v>
+        <v>5.65</v>
       </c>
       <c r="W33" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="Z33" t="n">
-        <v>7.7</v>
+        <v>4.17</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.22</v>
+        <v>1.72</v>
       </c>
       <c r="AB33" t="n">
-        <v>3.5</v>
+        <v>2.05</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.7</v>
+        <v>2.85</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.06</v>
+        <v>1.38</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.02</v>
+        <v>1.87</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46052.60416666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.5</v>
+        <v>9.85</v>
       </c>
       <c r="M35" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="O35" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="P35" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V35" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB35" t="n">
         <v>3.5</v>
       </c>
-      <c r="N35" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O35" t="n">
-        <v>3</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V35" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X35" t="n">
+      <c r="AC35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AH35" t="n">
         <v>1.02</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.45</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46052.60416666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="M36" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="O36" t="n">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="P36" t="n">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.21</v>
+        <v>2.85</v>
       </c>
       <c r="R36" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S36" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="T36" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="U36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="AA36" t="n">
         <v>1.47</v>
       </c>
-      <c r="V36" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AB36" t="n">
-        <v>2.05</v>
+        <v>2.53</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.85</v>
+        <v>2.27</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.16</v>
+        <v>2.63</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.87</v>
+        <v>1.45</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46052.60416666666</v>
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="M37" t="n">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="N37" t="n">
-        <v>6.84</v>
+        <v>6</v>
       </c>
       <c r="O37" t="n">
         <v>2.11</v>
@@ -4839,7 +4839,7 @@
         <v>2</v>
       </c>
       <c r="Q37" t="n">
-        <v>7.5</v>
+        <v>5.22</v>
       </c>
       <c r="R37" t="n">
         <v>1.47</v>
@@ -4848,7 +4848,7 @@
         <v>2.44</v>
       </c>
       <c r="T37" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="U37" t="n">
         <v>1.29</v>
@@ -4860,16 +4860,16 @@
         <v>1.02</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y37" t="n">
         <v>1.42</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AB37" t="n">
         <v>1.62</v>
@@ -4881,16 +4881,16 @@
         <v>1.17</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46052.625</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.22</v>
+        <v>2</v>
       </c>
       <c r="M38" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="N38" t="n">
-        <v>2.41</v>
+        <v>4.5</v>
       </c>
       <c r="O38" t="n">
-        <v>4.39</v>
+        <v>2.93</v>
       </c>
       <c r="P38" t="n">
         <v>1.77</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>6.21</v>
       </c>
       <c r="R38" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="S38" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="T38" t="n">
-        <v>3.45</v>
+        <v>4.33</v>
       </c>
       <c r="U38" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="V38" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="W38" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X38" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.52</v>
+        <v>1.76</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.39</v>
+        <v>2.04</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.49</v>
+        <v>3.39</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="AC38" t="n">
-        <v>4.7</v>
+        <v>7.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AE38" t="n">
-        <v>2.09</v>
+        <v>2.64</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.27</v>
+        <v>1.77</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46052.625</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.6</v>
+        <v>3.22</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="N39" t="n">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="O39" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q39" t="n">
         <v>3</v>
       </c>
-      <c r="P39" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.88</v>
-      </c>
       <c r="R39" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="S39" t="n">
-        <v>3.12</v>
+        <v>2.15</v>
       </c>
       <c r="T39" t="n">
-        <v>2.36</v>
+        <v>3.45</v>
       </c>
       <c r="U39" t="n">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="V39" t="n">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W39" t="n">
+        <v>1</v>
+      </c>
+      <c r="X39" t="n">
         <v>1.09</v>
       </c>
-      <c r="X39" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y39" t="n">
-        <v>1.16</v>
+        <v>1.52</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.05</v>
+        <v>2.39</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.66</v>
+        <v>2.49</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.15</v>
+        <v>1.46</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.61</v>
+        <v>4.7</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.55</v>
+        <v>2.09</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46052.625</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="M40" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>4.5</v>
+        <v>2.25</v>
       </c>
       <c r="O40" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>1.77</v>
+        <v>2.38</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.21</v>
+        <v>2.88</v>
       </c>
       <c r="R40" t="n">
-        <v>1.74</v>
+        <v>1.29</v>
       </c>
       <c r="S40" t="n">
-        <v>1.93</v>
+        <v>3.12</v>
       </c>
       <c r="T40" t="n">
-        <v>4.33</v>
+        <v>2.36</v>
       </c>
       <c r="U40" t="n">
-        <v>1.13</v>
+        <v>1.49</v>
       </c>
       <c r="V40" t="n">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="W40" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X40" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.76</v>
+        <v>1.16</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.04</v>
+        <v>4.05</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.39</v>
+        <v>1.66</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.26</v>
+        <v>2.15</v>
       </c>
       <c r="AC40" t="n">
-        <v>7.5</v>
+        <v>2.61</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.07</v>
+        <v>1.42</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.64</v>
+        <v>1.55</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.42</v>
+        <v>2.3</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.77</v>
+        <v>1.39</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46052.625</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.34</v>
+        <v>3.2</v>
       </c>
       <c r="M41" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N41" t="n">
-        <v>3.05</v>
+        <v>2.12</v>
       </c>
       <c r="O41" t="n">
-        <v>3.17</v>
+        <v>3.86</v>
       </c>
       <c r="P41" t="n">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.72</v>
+        <v>2.66</v>
       </c>
       <c r="R41" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="S41" t="n">
-        <v>2.64</v>
+        <v>2.9</v>
       </c>
       <c r="T41" t="n">
-        <v>3.31</v>
+        <v>2.56</v>
       </c>
       <c r="U41" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V41" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH41" t="n">
         <v>1.28</v>
-      </c>
-      <c r="V41" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46052.64583333334</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="M42" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="N42" t="n">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="O42" t="n">
-        <v>3.86</v>
+        <v>3</v>
       </c>
       <c r="P42" t="n">
-        <v>2.13</v>
+        <v>1.86</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.66</v>
+        <v>3.7</v>
       </c>
       <c r="R42" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="S42" t="n">
-        <v>2.9</v>
+        <v>2.31</v>
       </c>
       <c r="T42" t="n">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="U42" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="V42" t="n">
-        <v>5.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W42" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X42" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.58</v>
+        <v>2.62</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.78</v>
+        <v>2.27</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.97</v>
+        <v>1.56</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.94</v>
+        <v>4.32</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.14</v>
+        <v>1.76</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.28</v>
+        <v>1.54</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46052.64583333334</v>
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="M43" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="N43" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="O43" t="n">
         <v>3.49</v>
@@ -5556,10 +5556,10 @@
         <v>3.46</v>
       </c>
       <c r="R43" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="S43" t="n">
-        <v>2.29</v>
+        <v>2.52</v>
       </c>
       <c r="T43" t="n">
         <v>3.25</v>
@@ -5592,7 +5592,7 @@
         <v>4.2</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AE43" t="n">
         <v>1.94</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.24</v>
+        <v>3.25</v>
       </c>
       <c r="M44" t="n">
-        <v>3.37</v>
+        <v>3</v>
       </c>
       <c r="N44" t="n">
-        <v>2.66</v>
+        <v>2.15</v>
       </c>
       <c r="O44" t="n">
-        <v>2.45</v>
+        <v>4.27</v>
       </c>
       <c r="P44" t="n">
-        <v>2.42</v>
+        <v>2.06</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.12</v>
+        <v>2.86</v>
       </c>
       <c r="R44" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V44" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG44" t="n">
         <v>1.28</v>
       </c>
-      <c r="S44" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V44" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH44" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46052.64583333334</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5772,77 +5772,77 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46052.64583333334</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.35</v>
+        <v>1.36</v>
       </c>
       <c r="M46" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="N46" t="n">
-        <v>2.08</v>
+        <v>7</v>
       </c>
       <c r="O46" t="n">
-        <v>4.27</v>
+        <v>1.91</v>
       </c>
       <c r="P46" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="Q46" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T46" t="n">
         <v>2.9</v>
       </c>
-      <c r="R46" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S46" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T46" t="n">
-        <v>3.18</v>
-      </c>
       <c r="U46" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="V46" t="n">
-        <v>8.5</v>
+        <v>6.55</v>
       </c>
       <c r="W46" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.23</v>
+        <v>1.89</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="AC46" t="n">
-        <v>4.05</v>
+        <v>3.14</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.3</v>
+        <v>2.64</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46052.64583333334</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="M47" t="n">
-        <v>3.1</v>
+        <v>3.37</v>
       </c>
       <c r="N47" t="n">
-        <v>3.7</v>
+        <v>2.66</v>
       </c>
       <c r="O47" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="P47" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.85</v>
+        <v>3.12</v>
       </c>
       <c r="R47" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="S47" t="n">
-        <v>2.56</v>
+        <v>3.18</v>
       </c>
       <c r="T47" t="n">
-        <v>3.14</v>
+        <v>2.3</v>
       </c>
       <c r="U47" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="V47" t="n">
-        <v>8</v>
+        <v>5.25</v>
       </c>
       <c r="W47" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X47" t="n">
         <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.92</v>
+        <v>4.4</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.06</v>
+        <v>1.58</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.7</v>
+        <v>2.23</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.58</v>
+        <v>2.48</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.87</v>
+        <v>1.49</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.79</v>
+        <v>2.42</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46052.64583333334</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,77 +6129,77 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46052.64583333334</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.41</v>
+        <v>2.4</v>
       </c>
       <c r="M49" t="n">
-        <v>4.05</v>
+        <v>3</v>
       </c>
       <c r="N49" t="n">
-        <v>7</v>
+        <v>2.75</v>
       </c>
       <c r="O49" t="n">
-        <v>1.91</v>
+        <v>3.17</v>
       </c>
       <c r="P49" t="n">
-        <v>2.24</v>
+        <v>1.92</v>
       </c>
       <c r="Q49" t="n">
-        <v>7</v>
+        <v>3.72</v>
       </c>
       <c r="R49" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="S49" t="n">
-        <v>2.78</v>
+        <v>2.47</v>
       </c>
       <c r="T49" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V49" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z49" t="n">
         <v>2.74</v>
       </c>
-      <c r="U49" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V49" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AA49" t="n">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.14</v>
+        <v>4.08</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AE49" t="n">
-        <v>2.12</v>
+        <v>1.86</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AH49" t="n">
-        <v>2.64</v>
+        <v>1.44</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46052.64583333334</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.29</v>
+        <v>1.86</v>
       </c>
       <c r="M50" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="O50" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="P50" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="R50" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="S50" t="n">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="T50" t="n">
-        <v>3.25</v>
+        <v>3.02</v>
       </c>
       <c r="U50" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="V50" t="n">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="W50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X50" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AC50" t="n">
-        <v>4.32</v>
+        <v>3.72</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AF50" t="n">
         <v>1.76</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46052.64583333334</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="M54" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N54" t="n">
-        <v>2.12</v>
+        <v>3.25</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46052.66666666666</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M55" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O55" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="P55" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V55" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA55" t="n">
         <v>2</v>
       </c>
-      <c r="M55" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N55" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O55" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P55" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S55" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="T55" t="n">
+      <c r="AB55" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF55" t="n">
         <v>2</v>
       </c>
-      <c r="U55" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V55" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X55" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>2.56</v>
-      </c>
       <c r="AG55" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7094,64 +7094,64 @@
         <v>2.9</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,73 +7323,73 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="M58" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="N58" t="n">
-        <v>5</v>
+        <v>2.05</v>
       </c>
       <c r="O58" t="n">
-        <v>2.02</v>
+        <v>3.5</v>
       </c>
       <c r="P58" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="Q58" t="n">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="R58" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="S58" t="n">
-        <v>3.52</v>
+        <v>3.08</v>
       </c>
       <c r="T58" t="n">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="U58" t="n">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="V58" t="n">
-        <v>4.8</v>
+        <v>5.15</v>
       </c>
       <c r="W58" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X58" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z58" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA58" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD58" t="n">
         <v>1.44</v>
       </c>
-      <c r="AB58" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AE58" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AF58" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AH58" t="n">
-        <v>2.35</v>
+        <v>1.28</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,73 +7442,73 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>4.1</v>
+        <v>2.68</v>
       </c>
       <c r="M59" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N59" t="n">
-        <v>1.86</v>
+        <v>2.63</v>
       </c>
       <c r="O59" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="P59" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.42</v>
+        <v>2.93</v>
       </c>
       <c r="R59" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S59" t="n">
-        <v>3.22</v>
+        <v>2.7</v>
       </c>
       <c r="T59" t="n">
-        <v>2.38</v>
+        <v>2.82</v>
       </c>
       <c r="U59" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="V59" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W59" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X59" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z59" t="n">
-        <v>4.5</v>
+        <v>3.24</v>
       </c>
       <c r="AA59" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB59" t="n">
         <v>1.83</v>
       </c>
-      <c r="AB59" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AC59" t="n">
-        <v>2.54</v>
+        <v>3.25</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AF59" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AI59" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,73 +7561,73 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="M60" t="n">
-        <v>3</v>
+        <v>5.95</v>
       </c>
       <c r="N60" t="n">
-        <v>3.25</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O60" t="n">
-        <v>2.8</v>
+        <v>1.62</v>
       </c>
       <c r="P60" t="n">
-        <v>2</v>
+        <v>2.91</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.18</v>
+        <v>6.7</v>
       </c>
       <c r="R60" t="n">
-        <v>1.53</v>
+        <v>1.15</v>
       </c>
       <c r="S60" t="n">
-        <v>2.34</v>
+        <v>4.45</v>
       </c>
       <c r="T60" t="n">
-        <v>3.25</v>
+        <v>1.88</v>
       </c>
       <c r="U60" t="n">
-        <v>1.26</v>
+        <v>1.85</v>
       </c>
       <c r="V60" t="n">
-        <v>9.199999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="W60" t="n">
-        <v>1</v>
+        <v>1.23</v>
       </c>
       <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AG60" t="n">
         <v>1.1</v>
       </c>
-      <c r="Y60" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE60" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH60" t="n">
-        <v>1.58</v>
+        <v>3.95</v>
       </c>
       <c r="AI60" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,73 +7680,73 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="M61" t="n">
-        <v>3.2</v>
+        <v>3.88</v>
       </c>
       <c r="N61" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="O61" t="n">
-        <v>2.54</v>
+        <v>2.1</v>
       </c>
       <c r="P61" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S61" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V61" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="W61" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X61" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF61" t="n">
         <v>2.21</v>
       </c>
-      <c r="Q61" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="R61" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S61" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T61" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U61" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V61" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W61" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X61" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD61" t="n">
+      <c r="AG61" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE61" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH61" t="n">
-        <v>1.61</v>
+        <v>2.01</v>
       </c>
       <c r="AI61" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,73 +7799,73 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.72</v>
+        <v>4.1</v>
       </c>
       <c r="M62" t="n">
-        <v>3.88</v>
+        <v>3.45</v>
       </c>
       <c r="N62" t="n">
-        <v>4.33</v>
+        <v>1.86</v>
       </c>
       <c r="O62" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="P62" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.4</v>
+        <v>2.42</v>
       </c>
       <c r="R62" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S62" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="T62" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="U62" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="V62" t="n">
-        <v>5.15</v>
+        <v>5.5</v>
       </c>
       <c r="W62" t="n">
         <v>1.1</v>
       </c>
       <c r="X62" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z62" t="n">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="AC62" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AF62" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AG62" t="n">
         <v>1.25</v>
       </c>
       <c r="AH62" t="n">
-        <v>2.01</v>
+        <v>1.29</v>
       </c>
       <c r="AI62" s="3" t="n">
         <v>46052.66666666666</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,73 +7918,73 @@
         </is>
       </c>
       <c r="L63" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="M63" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N63" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O63" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P63" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S63" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V63" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AD63" t="n">
         <v>1.25</v>
       </c>
-      <c r="M63" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="N63" t="n">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="O63" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="P63" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="R63" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S63" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="T63" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U63" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V63" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="W63" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AE63" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AF63" t="n">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="AG63" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AH63" t="n">
-        <v>3.95</v>
+        <v>1.25</v>
       </c>
       <c r="AI63" s="3" t="n">
         <v>46052.66666666666</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,73 +8037,73 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="M64" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N64" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="O64" t="n">
-        <v>2.74</v>
+        <v>2.45</v>
       </c>
       <c r="P64" t="n">
-        <v>2.13</v>
+        <v>2.32</v>
       </c>
       <c r="Q64" t="n">
-        <v>4</v>
+        <v>3.72</v>
       </c>
       <c r="R64" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="S64" t="n">
-        <v>2.65</v>
+        <v>3.44</v>
       </c>
       <c r="T64" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="U64" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="V64" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="W64" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="X64" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="Z64" t="n">
-        <v>2.89</v>
+        <v>4.75</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.15</v>
+        <v>1.4</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.67</v>
+        <v>2.43</v>
       </c>
       <c r="AC64" t="n">
-        <v>3.78</v>
+        <v>2</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.19</v>
+        <v>1.59</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.87</v>
+        <v>1.45</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.83</v>
+        <v>2.56</v>
       </c>
       <c r="AG64" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AI64" s="3" t="n">
         <v>46052.66666666666</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,73 +8156,73 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.68</v>
+        <v>1.53</v>
       </c>
       <c r="M65" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="N65" t="n">
-        <v>2.63</v>
+        <v>5</v>
       </c>
       <c r="O65" t="n">
-        <v>3.2</v>
+        <v>2.02</v>
       </c>
       <c r="P65" t="n">
-        <v>2.24</v>
+        <v>2.45</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.93</v>
+        <v>5</v>
       </c>
       <c r="R65" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="S65" t="n">
-        <v>2.7</v>
+        <v>3.52</v>
       </c>
       <c r="T65" t="n">
-        <v>2.82</v>
+        <v>2.17</v>
       </c>
       <c r="U65" t="n">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
       <c r="V65" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="W65" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X65" t="n">
         <v>1.01</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z65" t="n">
-        <v>3.24</v>
+        <v>4.9</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.83</v>
+        <v>2.43</v>
       </c>
       <c r="AC65" t="n">
-        <v>3.25</v>
+        <v>2.28</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AF65" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.44</v>
+        <v>2.35</v>
       </c>
       <c r="AI65" s="3" t="n">
         <v>46052.66666666666</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,73 +8275,73 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.64</v>
+        <v>2.02</v>
       </c>
       <c r="M66" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N66" t="n">
-        <v>1.95</v>
+        <v>3.75</v>
       </c>
       <c r="O66" t="n">
-        <v>4.3</v>
+        <v>2.74</v>
       </c>
       <c r="P66" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="R66" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S66" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U66" t="n">
         <v>1.36</v>
       </c>
-      <c r="S66" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T66" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U66" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V66" t="n">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="W66" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X66" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z66" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC66" t="n">
-        <v>3.44</v>
+        <v>3.78</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.25</v>
+        <v>1.72</v>
       </c>
       <c r="AI66" s="3" t="n">
         <v>46052.66666666666</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,73 +8394,73 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="M67" t="n">
-        <v>3.12</v>
+        <v>3.38</v>
       </c>
       <c r="N67" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="O67" t="n">
-        <v>2.84</v>
+        <v>3.06</v>
       </c>
       <c r="P67" t="n">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R67" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="S67" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="T67" t="n">
-        <v>2.66</v>
+        <v>2.27</v>
       </c>
       <c r="U67" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="V67" t="n">
-        <v>6.55</v>
+        <v>5.1</v>
       </c>
       <c r="W67" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X67" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z67" t="n">
-        <v>3.42</v>
+        <v>4.55</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.87</v>
+        <v>2.29</v>
       </c>
       <c r="AC67" t="n">
-        <v>2.97</v>
+        <v>2.3</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="AF67" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="AG67" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AI67" s="3" t="n">
         <v>46052.67708333334</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,73 +8513,73 @@
         </is>
       </c>
       <c r="L68" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M68" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N68" t="n">
         <v>2.59</v>
       </c>
-      <c r="M68" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="N68" t="n">
-        <v>2.53</v>
-      </c>
       <c r="O68" t="n">
-        <v>3.06</v>
+        <v>2.84</v>
       </c>
       <c r="P68" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="Q68" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="R68" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="S68" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="T68" t="n">
-        <v>2.27</v>
+        <v>2.66</v>
       </c>
       <c r="U68" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V68" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH68" t="n">
         <v>1.53</v>
-      </c>
-      <c r="V68" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W68" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X68" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AE68" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AF68" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG68" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AH68" t="n">
-        <v>1.42</v>
       </c>
       <c r="AI68" s="3" t="n">
         <v>46052.67708333334</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,73 +8632,73 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI69" s="3" t="n">
         <v>46052.6875</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,73 +8751,73 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD70" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI70" s="3" t="n">
         <v>46052.6875</v>
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,73 +8989,73 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI72" s="3" t="n">
         <v>46052.6875</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,73 +9227,73 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.22</v>
+        <v>3.4</v>
       </c>
       <c r="M74" t="n">
-        <v>3.56</v>
+        <v>3.1</v>
       </c>
       <c r="N74" t="n">
-        <v>2.95</v>
+        <v>2.15</v>
       </c>
       <c r="O74" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="P74" t="n">
-        <v>2.27</v>
+        <v>1.92</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.68</v>
+        <v>2.8</v>
       </c>
       <c r="R74" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="S74" t="n">
-        <v>3.42</v>
+        <v>2.61</v>
       </c>
       <c r="T74" t="n">
-        <v>2.39</v>
+        <v>3.1</v>
       </c>
       <c r="U74" t="n">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="V74" t="n">
-        <v>5.5</v>
+        <v>9.1</v>
       </c>
       <c r="W74" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="X74" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="Z74" t="n">
-        <v>4.65</v>
+        <v>2.88</v>
       </c>
       <c r="AA74" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AB74" t="n">
         <v>1.6</v>
       </c>
-      <c r="AB74" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AC74" t="n">
-        <v>2.55</v>
+        <v>4.2</v>
       </c>
       <c r="AD74" t="n">
-        <v>1.49</v>
+        <v>1.16</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.5</v>
+        <v>1.94</v>
       </c>
       <c r="AF74" t="n">
-        <v>2.45</v>
+        <v>1.77</v>
       </c>
       <c r="AG74" t="n">
         <v>1.36</v>
       </c>
       <c r="AH74" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AI74" s="3" t="n">
         <v>46052.6875</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,73 +9346,73 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.66</v>
+        <v>3.65</v>
       </c>
       <c r="M75" t="n">
-        <v>3.52</v>
+        <v>3.29</v>
       </c>
       <c r="N75" t="n">
-        <v>4.3</v>
+        <v>2.03</v>
       </c>
       <c r="O75" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U75" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V75" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X75" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AC75" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD75" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH75" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AI75" s="3" t="n">
         <v>46052.6875</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,73 +9465,73 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="M76" t="n">
-        <v>4.84</v>
+        <v>3.3</v>
       </c>
       <c r="N76" t="n">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="O76" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P76" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S76" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V76" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W76" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X76" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH76" t="n">
         <v>1.91</v>
-      </c>
-      <c r="P76" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="R76" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S76" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T76" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U76" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V76" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W76" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X76" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA76" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB76" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC76" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE76" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF76" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG76" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH76" t="n">
-        <v>2.8</v>
       </c>
       <c r="AI76" s="3" t="n">
         <v>46052.69791666666</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,73 +9584,73 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="M77" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N77" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O77" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="P77" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Q77" t="n">
-        <v>5.11</v>
+        <v>4.8</v>
       </c>
       <c r="R77" t="n">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="S77" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="T77" t="n">
-        <v>2.88</v>
+        <v>3.82</v>
       </c>
       <c r="U77" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="V77" t="n">
-        <v>7.5</v>
+        <v>10.5</v>
       </c>
       <c r="W77" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X77" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="Z77" t="n">
-        <v>3.2</v>
+        <v>2.53</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.77</v>
+        <v>1.49</v>
       </c>
       <c r="AC77" t="n">
-        <v>3.1</v>
+        <v>5.25</v>
       </c>
       <c r="AD77" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AG77" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AI77" s="3" t="n">
         <v>46052.69791666666</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,73 +9703,73 @@
         </is>
       </c>
       <c r="L78" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="M78" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N78" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O78" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P78" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="R78" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S78" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V78" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W78" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X78" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AF78" t="n">
         <v>2.05</v>
       </c>
-      <c r="M78" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N78" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O78" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P78" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R78" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S78" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T78" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="U78" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V78" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="W78" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X78" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y78" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z78" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AA78" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB78" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC78" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AD78" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE78" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF78" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AG78" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.81</v>
+        <v>1.45</v>
       </c>
       <c r="AI78" s="3" t="n">
         <v>46052.69791666666</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,73 +9822,73 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.77</v>
+        <v>1.42</v>
       </c>
       <c r="M79" t="n">
-        <v>3.05</v>
+        <v>4.84</v>
       </c>
       <c r="N79" t="n">
-        <v>2.32</v>
+        <v>8.5</v>
       </c>
       <c r="O79" t="n">
-        <v>3.2</v>
+        <v>1.91</v>
       </c>
       <c r="P79" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.26</v>
+        <v>6.7</v>
       </c>
       <c r="R79" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="S79" t="n">
-        <v>2.77</v>
+        <v>3.35</v>
       </c>
       <c r="T79" t="n">
-        <v>2.77</v>
+        <v>2.49</v>
       </c>
       <c r="U79" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V79" t="n">
-        <v>6.7</v>
+        <v>5.4</v>
       </c>
       <c r="W79" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X79" t="n">
         <v>1.01</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="Z79" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="AC79" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="AD79" t="n">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="AF79" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG79" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.45</v>
+        <v>2.8</v>
       </c>
       <c r="AI79" s="3" t="n">
         <v>46052.69791666666</v>
@@ -10298,73 +10298,73 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AI83" s="3" t="n">
         <v>46052.83333333334</v>

--- a/jogos_2026-01-30.xlsx
+++ b/jogos_2026-01-30.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="M2" t="n">
-        <v>3.88</v>
+        <v>3.74</v>
       </c>
       <c r="N2" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O2" t="n">
         <v>4.15</v>
@@ -677,10 +677,10 @@
         <v>2.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="T2" t="n">
         <v>2.73</v>
@@ -692,22 +692,22 @@
         <v>6.9</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z2" t="n">
         <v>3.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
         <v>3.18</v>
@@ -719,7 +719,7 @@
         <v>1.7</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AG2" t="n">
         <v>1.26</v>
@@ -790,25 +790,25 @@
         <v>2.95</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.46</v>
+        <v>3.07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
         <v>2.56</v>
       </c>
       <c r="T3" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U3" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="V3" t="n">
-        <v>7</v>
+        <v>6.65</v>
       </c>
       <c r="W3" t="n">
         <v>1.05</v>
@@ -817,7 +817,7 @@
         <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z3" t="n">
         <v>3.35</v>
@@ -826,10 +826,10 @@
         <v>1.98</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.32</v>
+        <v>2.95</v>
       </c>
       <c r="AD3" t="n">
         <v>1.3</v>
@@ -841,10 +841,10 @@
         <v>2.05</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46052.22916666666</v>
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="M4" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
         <v>1.82</v>
@@ -912,7 +912,7 @@
         <v>2.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="R4" t="n">
         <v>1.36</v>
@@ -921,7 +921,7 @@
         <v>2.75</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U4" t="n">
         <v>1.4</v>
@@ -936,7 +936,7 @@
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z4" t="n">
         <v>3.42</v>
@@ -948,7 +948,7 @@
         <v>1.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AD4" t="n">
         <v>1.32</v>
@@ -957,13 +957,13 @@
         <v>1.69</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.79</v>
+        <v>1.24</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46052.22916666666</v>
@@ -1022,16 +1022,16 @@
         <v>3.8</v>
       </c>
       <c r="N5" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O5" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="P5" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R5" t="n">
         <v>1.22</v>
@@ -1055,7 +1055,7 @@
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
         <v>5.32</v>
@@ -1064,7 +1064,7 @@
         <v>1.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC5" t="n">
         <v>2.25</v>
@@ -1079,10 +1079,10 @@
         <v>2.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46052.23263888889</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2096,22 +2096,22 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="P14" t="n">
-        <v>2.23</v>
+        <v>2.37</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.6</v>
+        <v>5.41</v>
       </c>
       <c r="R14" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
         <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="U14" t="n">
         <v>1.41</v>
@@ -2132,28 +2132,28 @@
         <v>3.64</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AB14" t="n">
         <v>1.93</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AG14" t="n">
         <v>1.18</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46052.45138888889</v>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="M16" t="n">
-        <v>4.2</v>
+        <v>4.47</v>
       </c>
       <c r="N16" t="n">
         <v>5.61</v>
@@ -2343,7 +2343,7 @@
         <v>5.72</v>
       </c>
       <c r="R16" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S16" t="n">
         <v>3.58</v>
@@ -2352,10 +2352,10 @@
         <v>2.16</v>
       </c>
       <c r="U16" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="V16" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="W16" t="n">
         <v>1.12</v>
@@ -2364,7 +2364,7 @@
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="Z16" t="n">
         <v>5.3</v>
@@ -2379,7 +2379,7 @@
         <v>2.15</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AE16" t="n">
         <v>1.57</v>
@@ -2388,13 +2388,13 @@
         <v>2.23</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46052.47916666666</v>
+        <v>46052.48958333334</v>
       </c>
     </row>
     <row r="17">
@@ -2444,22 +2444,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="M17" t="n">
         <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O17" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="P17" t="n">
         <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="R17" t="n">
         <v>1.29</v>
@@ -2468,7 +2468,7 @@
         <v>3.12</v>
       </c>
       <c r="T17" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="U17" t="n">
         <v>1.47</v>
@@ -2480,7 +2480,7 @@
         <v>1.12</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
         <v>1.16</v>
@@ -2489,28 +2489,28 @@
         <v>4.15</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
         <v>2.23</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46052.5</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46052.5</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>6.37</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46052.5</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46052.5</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>6.59</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46052.5</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3286,55 +3286,55 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.4</v>
+        <v>5.37</v>
       </c>
       <c r="R24" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="T24" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="U24" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V24" t="n">
-        <v>7.1</v>
+        <v>6.4</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AF24" t="n">
         <v>1.82</v>
@@ -3343,7 +3343,7 @@
         <v>1.21</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46052.53472222222</v>
@@ -3355,7 +3355,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46052.5625</v>
+        <v>46052.57291666666</v>
       </c>
     </row>
     <row r="26">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,61 +3515,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="N26" t="n">
-        <v>2.95</v>
+        <v>2.49</v>
       </c>
       <c r="O26" t="n">
-        <v>2.88</v>
+        <v>3.56</v>
       </c>
       <c r="P26" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.65</v>
+        <v>3.04</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S26" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="T26" t="n">
-        <v>3.07</v>
+        <v>3.15</v>
       </c>
       <c r="U26" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V26" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="W26" t="n">
         <v>1.03</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE26" t="n">
         <v>1.8</v>
@@ -3578,10 +3578,10 @@
         <v>1.9</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46052.58333333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.9</v>
+        <v>3.76</v>
       </c>
       <c r="M27" t="n">
-        <v>3.24</v>
+        <v>3.57</v>
       </c>
       <c r="N27" t="n">
-        <v>2.49</v>
+        <v>1.96</v>
       </c>
       <c r="O27" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="P27" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.04</v>
+        <v>2.55</v>
       </c>
       <c r="R27" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="T27" t="n">
-        <v>3.02</v>
+        <v>2.73</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>7.6</v>
+        <v>6.65</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AE27" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46052.58333333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.07</v>
+        <v>2.2</v>
       </c>
       <c r="M28" t="n">
-        <v>10</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>16.53</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.32</v>
+        <v>2.88</v>
       </c>
       <c r="P28" t="n">
-        <v>3.95</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>13</v>
+        <v>3.67</v>
       </c>
       <c r="R28" t="n">
-        <v>1.15</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>5.3</v>
+        <v>2.77</v>
       </c>
       <c r="T28" t="n">
-        <v>1.69</v>
+        <v>2.9</v>
       </c>
       <c r="U28" t="n">
-        <v>2.01</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z28" t="n">
         <v>3.14</v>
       </c>
-      <c r="W28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>9.300000000000001</v>
-      </c>
       <c r="AA28" t="n">
-        <v>1.18</v>
+        <v>2.05</v>
       </c>
       <c r="AB28" t="n">
-        <v>4.2</v>
+        <v>1.74</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.49</v>
+        <v>3.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="AH28" t="n">
-        <v>6.8</v>
+        <v>1.56</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46052.58333333334</v>
@@ -3890,10 +3890,10 @@
         <v>2.34</v>
       </c>
       <c r="R29" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S29" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="T29" t="n">
         <v>2.99</v>
@@ -3911,19 +3911,19 @@
         <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z29" t="n">
         <v>2.83</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AB29" t="n">
         <v>1.66</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.58</v>
+        <v>3.84</v>
       </c>
       <c r="AD29" t="n">
         <v>1.21</v>
@@ -3935,10 +3935,10 @@
         <v>1.73</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46052.58333333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.76</v>
+        <v>1.07</v>
       </c>
       <c r="M30" t="n">
-        <v>3.57</v>
+        <v>10</v>
       </c>
       <c r="N30" t="n">
-        <v>1.96</v>
+        <v>16.53</v>
       </c>
       <c r="O30" t="n">
-        <v>4.25</v>
+        <v>1.32</v>
       </c>
       <c r="P30" t="n">
-        <v>2.13</v>
+        <v>3.89</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.55</v>
+        <v>13</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="S30" t="n">
-        <v>2.88</v>
+        <v>5.3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.73</v>
+        <v>1.7</v>
       </c>
       <c r="U30" t="n">
-        <v>1.4</v>
+        <v>2.01</v>
       </c>
       <c r="V30" t="n">
-        <v>6.65</v>
+        <v>3.14</v>
       </c>
       <c r="W30" t="n">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="X30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.24</v>
+        <v>1</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.38</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.94</v>
+        <v>1.17</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.94</v>
+        <v>4</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.18</v>
+        <v>1.49</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.29</v>
+        <v>2.27</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.01</v>
+        <v>1.7</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.31</v>
+        <v>1.02</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.29</v>
+        <v>6.8</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46052.58333333334</v>
@@ -4113,19 +4113,19 @@
         <v>2.23</v>
       </c>
       <c r="M31" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="N31" t="n">
         <v>3.07</v>
       </c>
       <c r="O31" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="P31" t="n">
         <v>2.07</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.73</v>
+        <v>3.8</v>
       </c>
       <c r="R31" t="n">
         <v>1.38</v>
@@ -4140,31 +4140,31 @@
         <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>6.25</v>
+        <v>6.3</v>
       </c>
       <c r="W31" t="n">
         <v>1.06</v>
       </c>
       <c r="X31" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
         <v>1.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="AA31" t="n">
         <v>1.91</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AC31" t="n">
         <v>3.05</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE31" t="n">
         <v>1.68</v>
@@ -4173,7 +4173,7 @@
         <v>2.06</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
         <v>1.56</v>
@@ -4235,16 +4235,16 @@
         <v>3.6</v>
       </c>
       <c r="N32" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O32" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="P32" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>4.58</v>
       </c>
       <c r="R32" t="n">
         <v>1.3</v>
@@ -4253,7 +4253,7 @@
         <v>3.08</v>
       </c>
       <c r="T32" t="n">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="U32" t="n">
         <v>1.46</v>
@@ -4262,16 +4262,16 @@
         <v>5.8</v>
       </c>
       <c r="W32" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X32" t="n">
         <v>1.04</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z32" t="n">
-        <v>4.05</v>
+        <v>3.82</v>
       </c>
       <c r="AA32" t="n">
         <v>1.69</v>
@@ -4280,10 +4280,10 @@
         <v>2.04</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE32" t="n">
         <v>1.64</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46052.60416666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46052.60416666666</v>
@@ -4586,31 +4586,31 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>9.85</v>
+        <v>9.5</v>
       </c>
       <c r="M35" t="n">
-        <v>6.65</v>
+        <v>6.55</v>
       </c>
       <c r="N35" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="O35" t="n">
-        <v>7.39</v>
+        <v>7.04</v>
       </c>
       <c r="P35" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R35" t="n">
         <v>1.11</v>
       </c>
       <c r="S35" t="n">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="T35" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="U35" t="n">
         <v>1.9</v>
@@ -4625,34 +4625,34 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Z35" t="n">
         <v>7.7</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AB35" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AC35" t="n">
         <v>1.7</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AG35" t="n">
         <v>1.04</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46052.60416666666</v>
@@ -4708,13 +4708,13 @@
         <v>2.5</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="O36" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="P36" t="n">
         <v>2.28</v>
@@ -4729,13 +4729,13 @@
         <v>3.42</v>
       </c>
       <c r="T36" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="U36" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="V36" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="W36" t="n">
         <v>1.13</v>
@@ -4744,16 +4744,16 @@
         <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z36" t="n">
-        <v>5.47</v>
+        <v>4.85</v>
       </c>
       <c r="AA36" t="n">
         <v>1.47</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="AC36" t="n">
         <v>2.27</v>
@@ -4762,10 +4762,10 @@
         <v>1.63</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="AG36" t="n">
         <v>1.26</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="M37" t="n">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="N37" t="n">
-        <v>6</v>
+        <v>2.37</v>
       </c>
       <c r="O37" t="n">
-        <v>2.11</v>
+        <v>4.39</v>
       </c>
       <c r="P37" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.22</v>
+        <v>3.2</v>
       </c>
       <c r="R37" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S37" t="n">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="T37" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="U37" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V37" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W37" t="n">
-        <v>1.02</v>
+    